--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -1393,13 +1393,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.61463737268</v>
+        <v>46073.78130403935</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55695184028</v>
+        <v>46092.72361850695</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.65642046296</v>
+        <v>46112.823087129625</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1442,13 +1442,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.61463773148</v>
+        <v>46073.781304398144</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55691717593</v>
+        <v>46092.72358384259</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55695162037</v>
+        <v>46092.72361828704</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1507,13 +1507,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.61463802084</v>
+        <v>46073.7813046875</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.556917650465</v>
+        <v>46092.72358431713</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55695165509</v>
+        <v>46092.72361832176</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1572,13 +1572,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.61463835648</v>
+        <v>46073.78130502315</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55691803241</v>
+        <v>46092.72358469907</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55695146991</v>
+        <v>46092.72361813657</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1637,13 +1637,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.61463865741</v>
+        <v>46073.781305324075</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55691841435</v>
+        <v>46092.72358508102</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.52937359954</v>
+        <v>46100.69604026621</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1702,13 +1702,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.614638935185</v>
+        <v>46073.78130560185</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55691896991</v>
+        <v>46092.72358563657</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55695190972</v>
+        <v>46092.72361857639</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1767,13 +1767,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.61464047454</v>
+        <v>46073.7813071412</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.36058061343</v>
+        <v>46114.52724728009</v>
       </c>
       <c r="D10" s="5">
-        <v>46114.3605944213</v>
+        <v>46114.52726108796</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1820,13 +1820,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.61463789352</v>
+        <v>46073.78130456019</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.36049391204</v>
+        <v>46114.5271605787</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.36051359954</v>
+        <v>46114.5271802662</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1885,13 +1885,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.61463865741</v>
+        <v>46073.781305324075</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.36051849537</v>
+        <v>46114.527185162035</v>
       </c>
       <c r="D12" s="5">
-        <v>46114.36053143519</v>
+        <v>46114.52719810185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1950,13 +1950,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.61463895833</v>
+        <v>46073.781305625</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.36735673611</v>
+        <v>46097.53402340278</v>
       </c>
       <c r="D13" s="8">
-        <v>46097.36737695602</v>
+        <v>46097.53404362268</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -2015,13 +2015,13 @@
         <v>56</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.61463924768</v>
+        <v>46073.78130591435</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.360559837965</v>
+        <v>46114.52722650463</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.36058155092</v>
+        <v>46114.52724821759</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>57</v>
@@ -2080,13 +2080,13 @@
         <v>60</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.61463953704</v>
+        <v>46073.7813062037</v>
       </c>
       <c r="C15" s="8">
-        <v>46127.44410472222</v>
+        <v>46127.61077138889</v>
       </c>
       <c r="D15" s="8">
-        <v>46127.4441183912</v>
+        <v>46127.61078505787</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>61</v>
@@ -2133,13 +2133,13 @@
         <v>63</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.614640127314</v>
+        <v>46073.781306793986</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.36071721065</v>
+        <v>46114.527383877314</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.36073143518</v>
+        <v>46114.527398101854</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>64</v>
@@ -2198,13 +2198,13 @@
         <v>66</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.61463982639</v>
+        <v>46073.78130649305</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.360843194445</v>
+        <v>46114.52750986112</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.36085722222</v>
+        <v>46114.527523888886</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>67</v>
@@ -2263,13 +2263,13 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.614640694446</v>
+        <v>46073.78130736111</v>
       </c>
       <c r="C18" s="5">
-        <v>46127.44408350694</v>
+        <v>46127.61075017361</v>
       </c>
       <c r="D18" s="5">
-        <v>46127.44410570602</v>
+        <v>46127.61077237269</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -2328,13 +2328,13 @@
         <v>73</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.61463732639</v>
+        <v>46073.781303993055</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.367433287036</v>
+        <v>46097.5340999537</v>
       </c>
       <c r="D19" s="8">
-        <v>46100.54223155093</v>
+        <v>46100.70889821759</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>74</v>
@@ -2393,13 +2393,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.33391810185</v>
+        <v>46077.50058476852</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.36086756944</v>
+        <v>46114.52753423611</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.36088302083</v>
+        <v>46114.5275496875</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2458,13 +2458,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.61463765046</v>
+        <v>46073.78130431713</v>
       </c>
       <c r="C21" s="8">
-        <v>46169.65596876157</v>
+        <v>46169.82263542824</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.4976116551</v>
+        <v>46181.664278321754</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2507,13 +2507,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.61463792824</v>
+        <v>46073.78130459491</v>
       </c>
       <c r="C22" s="5">
-        <v>46157.604720104166</v>
+        <v>46157.77138677084</v>
       </c>
       <c r="D22" s="5">
-        <v>46157.6047322338</v>
+        <v>46157.77139890046</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2572,13 +2572,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.6146381713</v>
+        <v>46073.78130483796</v>
       </c>
       <c r="C23" s="8">
-        <v>46157.604641631944</v>
+        <v>46157.771308298616</v>
       </c>
       <c r="D23" s="8">
-        <v>46157.60464263889</v>
+        <v>46157.77130930556</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2633,13 +2633,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.61463840278</v>
+        <v>46073.781305069446</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.60470711805</v>
+        <v>46157.77137378472</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.60470844907</v>
+        <v>46157.77137511574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2694,13 +2694,13 @@
         <v>97</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.614639363426</v>
+        <v>46073.7813060301</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.604874675926</v>
+        <v>46157.77154134259</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.604885381945</v>
+        <v>46157.77155204861</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>
@@ -2759,13 +2759,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.61463960649</v>
+        <v>46073.781306273144</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.60482311343</v>
+        <v>46157.77148978009</v>
       </c>
       <c r="D26" s="5">
-        <v>46157.6048241088</v>
+        <v>46157.77149077546</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2820,13 +2820,13 @@
         <v>103</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.61463819444</v>
+        <v>46073.78130486111</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.60486304398</v>
+        <v>46157.77152971065</v>
       </c>
       <c r="D27" s="8">
-        <v>46157.60486414352</v>
+        <v>46157.77153081019</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>104</v>
@@ -2881,13 +2881,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.614638541665</v>
+        <v>46073.78130520834</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.60525976852</v>
+        <v>46157.77192643518</v>
       </c>
       <c r="D28" s="5">
-        <v>46170.01735829861</v>
+        <v>46170.184024965274</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -2946,13 +2946,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.61463885417</v>
+        <v>46073.78130552083</v>
       </c>
       <c r="C29" s="8">
-        <v>46157.60518351852</v>
+        <v>46157.771850185185</v>
       </c>
       <c r="D29" s="8">
-        <v>46157.60518459491</v>
+        <v>46157.771851261576</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>110</v>
@@ -3007,13 +3007,13 @@
         <v>112</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.61463913195</v>
+        <v>46073.781305798606</v>
       </c>
       <c r="C30" s="5">
-        <v>46157.6052255324</v>
+        <v>46157.771892199075</v>
       </c>
       <c r="D30" s="5">
-        <v>46157.60522657407</v>
+        <v>46157.771893240744</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -3068,13 +3068,13 @@
         <v>115</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.61463939815</v>
+        <v>46073.78130606482</v>
       </c>
       <c r="C31" s="8">
-        <v>46157.60524755787</v>
+        <v>46157.77191422453</v>
       </c>
       <c r="D31" s="8">
-        <v>46157.60524866898</v>
+        <v>46157.771915335645</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>116</v>
@@ -3129,13 +3129,13 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.6146396875</v>
+        <v>46073.78130635417</v>
       </c>
       <c r="C32" s="5">
-        <v>46113.37039376158</v>
+        <v>46113.537060428236</v>
       </c>
       <c r="D32" s="5">
-        <v>46113.37041113426</v>
+        <v>46113.537077800924</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3194,13 +3194,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.61463996528</v>
+        <v>46073.78130663194</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.367482581016</v>
+        <v>46097.53414924769</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.367483738424</v>
+        <v>46097.53415040509</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3255,13 +3255,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.61464025463</v>
+        <v>46073.7813069213</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.422227337964</v>
+        <v>46104.58889400463</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.42222903935</v>
+        <v>46104.58889570602</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3316,13 +3316,13 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.33398888889</v>
+        <v>46077.50065555556</v>
       </c>
       <c r="C35" s="8">
-        <v>46154.701581574074</v>
+        <v>46154.868248240746</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.497511608795</v>
+        <v>46181.66417827546</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3381,13 +3381,13 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.33456631945</v>
+        <v>46077.50123298611</v>
       </c>
       <c r="C36" s="5">
-        <v>46154.70076122685</v>
+        <v>46154.86742789352</v>
       </c>
       <c r="D36" s="5">
-        <v>46154.70076284722</v>
+        <v>46154.86742951389</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>80</v>
@@ -3436,13 +3436,13 @@
         <v>134</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.33469134259</v>
+        <v>46077.501358009264</v>
       </c>
       <c r="C37" s="8">
-        <v>46154.70129416666</v>
+        <v>46154.86796083333</v>
       </c>
       <c r="D37" s="8">
-        <v>46154.70129538194</v>
+        <v>46154.86796204861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>135</v>
@@ -3491,13 +3491,13 @@
         <v>137</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.614640520835</v>
+        <v>46073.7813071875</v>
       </c>
       <c r="C38" s="5">
-        <v>46175.5429012963</v>
+        <v>46175.709567962964</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.49767363426</v>
+        <v>46181.66434030092</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>138</v>
@@ -3540,13 +3540,13 @@
         <v>140</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.61464082176</v>
+        <v>46073.781307488425</v>
       </c>
       <c r="C39" s="8">
-        <v>46098.35299818287</v>
+        <v>46098.51966484953</v>
       </c>
       <c r="D39" s="8">
-        <v>46098.3530200463</v>
+        <v>46098.51968671296</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>141</v>
@@ -3605,13 +3605,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.61463748843</v>
+        <v>46073.7813041551</v>
       </c>
       <c r="C40" s="5">
-        <v>46107.555180509255</v>
+        <v>46107.721847175926</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.49777780093</v>
+        <v>46181.66444446759</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -3670,13 +3670,13 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46092.33831024305</v>
+        <v>46092.504976909724</v>
       </c>
       <c r="C41" s="8">
-        <v>46107.55534931713</v>
+        <v>46107.722015983796</v>
       </c>
       <c r="D41" s="8">
-        <v>46107.55536530093</v>
+        <v>46107.7220319676</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3735,13 +3735,13 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46092.33835142361</v>
+        <v>46092.505018090276</v>
       </c>
       <c r="C42" s="5">
-        <v>46175.54288180555</v>
+        <v>46175.70954847222</v>
       </c>
       <c r="D42" s="5">
-        <v>46178.007146516204</v>
+        <v>46178.173813182875</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>153</v>
@@ -3800,13 +3800,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.61463778935</v>
+        <v>46073.78130445602</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.610402754624</v>
+        <v>46127.777069421296</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.49773920139</v>
+        <v>46181.664405868054</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3849,13 +3849,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.61463805556</v>
+        <v>46073.78130472222</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.48092611111</v>
+        <v>46127.64759277778</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.481235659725</v>
+        <v>46127.64790232639</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -3914,13 +3914,13 @@
         <v>166</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.61463829861</v>
+        <v>46073.781304965276</v>
       </c>
       <c r="C45" s="8">
-        <v>46127.610388333334</v>
+        <v>46127.777055</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.61040306713</v>
+        <v>46127.7770697338</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>167</v>
@@ -3979,13 +3979,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.61463851852</v>
+        <v>46073.781305185184</v>
       </c>
       <c r="C46" s="5">
-        <v>46157.59841302084</v>
+        <v>46157.765079687495</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.49789353009</v>
+        <v>46181.66456019676</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4028,13 +4028,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.614638750005</v>
+        <v>46073.78130541666</v>
       </c>
       <c r="C47" s="8">
-        <v>46128.32995168981</v>
+        <v>46128.49661835648</v>
       </c>
       <c r="D47" s="8">
-        <v>46128.32996815973</v>
+        <v>46128.496634826384</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>175</v>
@@ -4093,13 +4093,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.6146390162</v>
+        <v>46073.781305682875</v>
       </c>
       <c r="C48" s="5">
-        <v>46149.72695866898</v>
+        <v>46149.89362533565</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.49785015047</v>
+        <v>46181.66451681713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4158,13 +4158,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.61463924768</v>
+        <v>46073.78130591435</v>
       </c>
       <c r="C49" s="8">
-        <v>46157.59775716435</v>
+        <v>46157.76442383102</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.4978709375</v>
+        <v>46181.66453760417</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4223,13 +4223,13 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.61463946759</v>
+        <v>46073.78130613426</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.605543032405</v>
+        <v>46157.77220969908</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.60560336805</v>
+        <v>46157.77227003472</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>159</v>
@@ -4272,13 +4272,13 @@
         <v>189</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.61463969907</v>
+        <v>46073.78130636574</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.60551525463</v>
+        <v>46157.7721819213</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.605530891204</v>
+        <v>46157.772197557875</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>190</v>
@@ -4337,13 +4337,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.61466482639</v>
+        <v>46073.78133149305</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.605521006946</v>
+        <v>46157.77218767361</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.60553671296</v>
+        <v>46157.77220337963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4402,13 +4402,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.61466519676</v>
+        <v>46073.78133186343</v>
       </c>
       <c r="C53" s="8">
-        <v>46157.60552734954</v>
+        <v>46157.7721940162</v>
       </c>
       <c r="D53" s="8">
-        <v>46172.03007071759</v>
+        <v>46172.19673738426</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4467,13 +4467,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.334089525466</v>
+        <v>46077.50075619213</v>
       </c>
       <c r="C54" s="5">
-        <v>46157.602643171296</v>
+        <v>46157.76930983797</v>
       </c>
       <c r="D54" s="5">
-        <v>46157.60265962963</v>
+        <v>46157.7693262963</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4532,13 +4532,13 @@
         <v>201</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.61466560185</v>
+        <v>46073.78133226852</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.462844803245</v>
+        <v>46181.6295114699</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.49799682871</v>
+        <v>46181.664663495365</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>202</v>
@@ -4581,13 +4581,13 @@
         <v>204</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.61466594908</v>
+        <v>46073.78133261574</v>
       </c>
       <c r="C56" s="5">
-        <v>46148.27235508102</v>
+        <v>46148.43902174769</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.49814753472</v>
+        <v>46181.66481420139</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>205</v>
@@ -4646,13 +4646,13 @@
         <v>208</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.61466634259</v>
+        <v>46073.78133300926</v>
       </c>
       <c r="C57" s="8">
-        <v>46148.27236634259</v>
+        <v>46148.43903300926</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.49818391204</v>
+        <v>46181.6648505787</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>209</v>
@@ -4711,13 +4711,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.61466681713</v>
+        <v>46073.7813334838</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.4627858912</v>
+        <v>46181.62945255787</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.46280165509</v>
+        <v>46181.62946832176</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4776,13 +4776,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.61466721065</v>
+        <v>46073.78133387731</v>
       </c>
       <c r="C59" s="8">
-        <v>46181.462830069446</v>
+        <v>46181.62949673611</v>
       </c>
       <c r="D59" s="8">
-        <v>46181.462844062495</v>
+        <v>46181.629510729166</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4841,13 +4841,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.336303993055</v>
+        <v>46077.50297065973</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.46280292824</v>
+        <v>46181.629469594904</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.46281909722</v>
+        <v>46181.629485763886</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4906,13 +4906,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.61466755787</v>
+        <v>46073.781334224535</v>
       </c>
       <c r="C61" s="8">
-        <v>46148.272386111115</v>
+        <v>46148.43905277778</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.49827096065</v>
+        <v>46181.66493762731</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>156</v>
@@ -4969,13 +4969,13 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.614667905094</v>
+        <v>46073.78133457176</v>
       </c>
       <c r="C62" s="5">
-        <v>46148.27240263889</v>
+        <v>46148.439069305554</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.4983139699</v>
+        <v>46181.664980636575</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>157</v>
@@ -5034,13 +5034,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.61464035879</v>
+        <v>46073.78130702546</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.46211253472</v>
+        <v>46181.62877920139</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.49848010417</v>
+        <v>46181.66514677083</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5083,13 +5083,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.614640740736</v>
+        <v>46073.78130740741</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.4620606713</v>
+        <v>46181.628727337964</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.4620774537</v>
+        <v>46181.628744120375</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5148,13 +5148,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.61464101852</v>
+        <v>46073.78130768519</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.46194850694</v>
+        <v>46181.62861517361</v>
       </c>
       <c r="D65" s="8">
-        <v>46183.04071021991</v>
+        <v>46183.207376886574</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5213,13 +5213,13 @@
         <v>235</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.61464130787</v>
+        <v>46073.78130797454</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.46202283565</v>
+        <v>46181.628689502315</v>
       </c>
       <c r="D66" s="5">
-        <v>46183.04071077546</v>
+        <v>46183.20737744213</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>236</v>
@@ -5278,13 +5278,13 @@
         <v>238</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.61464158565</v>
+        <v>46073.78130825231</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.46209758102</v>
+        <v>46181.62876424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.01260739584</v>
+        <v>46184.179274062495</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>239</v>
@@ -5343,11 +5343,11 @@
         <v>241</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.614641886576</v>
+        <v>46073.78130855324</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46092.34252207176</v>
+        <v>46092.509188738426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>242</v>
@@ -5390,11 +5390,11 @@
         <v>244</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.61464215278</v>
+        <v>46073.781308819445</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46185.01105320602</v>
+        <v>46185.177719872685</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>245</v>
@@ -5453,11 +5453,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.61464240741</v>
+        <v>46073.781309074075</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.011053159724</v>
+        <v>46185.17771982639</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>250</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46185.177719872685</v>
+        <v>46193.174377303236</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>245</v>
@@ -5438,8 +5438,8 @@
       <c r="R69" s="8">
         <v>46192</v>
       </c>
-      <c r="S69" s="12" t="s">
-        <v>207</v>
+      <c r="S69" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.17771982639</v>
+        <v>46193.17437732639</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>250</v>
@@ -5501,8 +5501,8 @@
       <c r="R70" s="5">
         <v>46192</v>
       </c>
-      <c r="S70" s="12" t="s">
-        <v>207</v>
+      <c r="S70" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46193.174377303236</v>
+        <v>46195.12549048611</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>245</v>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46193.17437732639</v>
+        <v>46195.12549313657</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>250</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -1393,13 +1393,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.78130403935</v>
+        <v>46073.61463737268</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72361850695</v>
+        <v>46092.55695184028</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.823087129625</v>
+        <v>46112.65642046296</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1442,13 +1442,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.781304398144</v>
+        <v>46073.61463773148</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72358384259</v>
+        <v>46092.55691717593</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72361828704</v>
+        <v>46092.55695162037</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1507,13 +1507,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.7813046875</v>
+        <v>46073.61463802084</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72358431713</v>
+        <v>46092.556917650465</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72361832176</v>
+        <v>46092.55695165509</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1572,13 +1572,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.78130502315</v>
+        <v>46073.61463835648</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72358469907</v>
+        <v>46092.55691803241</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72361813657</v>
+        <v>46092.55695146991</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1637,13 +1637,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.781305324075</v>
+        <v>46073.61463865741</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72358508102</v>
+        <v>46092.55691841435</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.69604026621</v>
+        <v>46100.52937359954</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1702,13 +1702,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.78130560185</v>
+        <v>46073.614638935185</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72358563657</v>
+        <v>46092.55691896991</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72361857639</v>
+        <v>46092.55695190972</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1767,13 +1767,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.7813071412</v>
+        <v>46073.61464047454</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.52724728009</v>
+        <v>46114.36058061343</v>
       </c>
       <c r="D10" s="5">
-        <v>46114.52726108796</v>
+        <v>46114.3605944213</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1820,13 +1820,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.78130456019</v>
+        <v>46073.61463789352</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.5271605787</v>
+        <v>46114.36049391204</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.5271802662</v>
+        <v>46114.36051359954</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1885,13 +1885,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.781305324075</v>
+        <v>46073.61463865741</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.527185162035</v>
+        <v>46114.36051849537</v>
       </c>
       <c r="D12" s="5">
-        <v>46114.52719810185</v>
+        <v>46114.36053143519</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1950,13 +1950,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.781305625</v>
+        <v>46073.61463895833</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.53402340278</v>
+        <v>46097.36735673611</v>
       </c>
       <c r="D13" s="8">
-        <v>46097.53404362268</v>
+        <v>46097.36737695602</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -2015,13 +2015,13 @@
         <v>56</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.78130591435</v>
+        <v>46073.61463924768</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.52722650463</v>
+        <v>46114.360559837965</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.52724821759</v>
+        <v>46114.36058155092</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>57</v>
@@ -2080,13 +2080,13 @@
         <v>60</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.7813062037</v>
+        <v>46073.61463953704</v>
       </c>
       <c r="C15" s="8">
-        <v>46127.61077138889</v>
+        <v>46127.44410472222</v>
       </c>
       <c r="D15" s="8">
-        <v>46127.61078505787</v>
+        <v>46127.4441183912</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>61</v>
@@ -2133,13 +2133,13 @@
         <v>63</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.781306793986</v>
+        <v>46073.614640127314</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.527383877314</v>
+        <v>46114.36071721065</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.527398101854</v>
+        <v>46114.36073143518</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>64</v>
@@ -2198,13 +2198,13 @@
         <v>66</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.78130649305</v>
+        <v>46073.61463982639</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.52750986112</v>
+        <v>46114.360843194445</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.527523888886</v>
+        <v>46114.36085722222</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>67</v>
@@ -2263,13 +2263,13 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.78130736111</v>
+        <v>46073.614640694446</v>
       </c>
       <c r="C18" s="5">
-        <v>46127.61075017361</v>
+        <v>46127.44408350694</v>
       </c>
       <c r="D18" s="5">
-        <v>46127.61077237269</v>
+        <v>46127.44410570602</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -2328,13 +2328,13 @@
         <v>73</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.781303993055</v>
+        <v>46073.61463732639</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.5340999537</v>
+        <v>46097.367433287036</v>
       </c>
       <c r="D19" s="8">
-        <v>46100.70889821759</v>
+        <v>46100.54223155093</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>74</v>
@@ -2393,13 +2393,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.50058476852</v>
+        <v>46077.33391810185</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.52753423611</v>
+        <v>46114.36086756944</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.5275496875</v>
+        <v>46114.36088302083</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2458,13 +2458,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.78130431713</v>
+        <v>46073.61463765046</v>
       </c>
       <c r="C21" s="8">
-        <v>46169.82263542824</v>
+        <v>46169.65596876157</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.664278321754</v>
+        <v>46181.4976116551</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2507,13 +2507,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.78130459491</v>
+        <v>46073.61463792824</v>
       </c>
       <c r="C22" s="5">
-        <v>46157.77138677084</v>
+        <v>46157.604720104166</v>
       </c>
       <c r="D22" s="5">
-        <v>46157.77139890046</v>
+        <v>46157.6047322338</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2572,13 +2572,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.78130483796</v>
+        <v>46073.6146381713</v>
       </c>
       <c r="C23" s="8">
-        <v>46157.771308298616</v>
+        <v>46157.604641631944</v>
       </c>
       <c r="D23" s="8">
-        <v>46157.77130930556</v>
+        <v>46157.60464263889</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2633,13 +2633,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.781305069446</v>
+        <v>46073.61463840278</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.77137378472</v>
+        <v>46157.60470711805</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.77137511574</v>
+        <v>46157.60470844907</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2694,13 +2694,13 @@
         <v>97</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.7813060301</v>
+        <v>46073.614639363426</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.77154134259</v>
+        <v>46157.604874675926</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.77155204861</v>
+        <v>46157.604885381945</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>
@@ -2759,13 +2759,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.781306273144</v>
+        <v>46073.61463960649</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.77148978009</v>
+        <v>46157.60482311343</v>
       </c>
       <c r="D26" s="5">
-        <v>46157.77149077546</v>
+        <v>46157.6048241088</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2820,13 +2820,13 @@
         <v>103</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.78130486111</v>
+        <v>46073.61463819444</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.77152971065</v>
+        <v>46157.60486304398</v>
       </c>
       <c r="D27" s="8">
-        <v>46157.77153081019</v>
+        <v>46157.60486414352</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>104</v>
@@ -2881,13 +2881,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.78130520834</v>
+        <v>46073.614638541665</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.77192643518</v>
+        <v>46157.60525976852</v>
       </c>
       <c r="D28" s="5">
-        <v>46170.184024965274</v>
+        <v>46170.01735829861</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -2946,13 +2946,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.78130552083</v>
+        <v>46073.61463885417</v>
       </c>
       <c r="C29" s="8">
-        <v>46157.771850185185</v>
+        <v>46157.60518351852</v>
       </c>
       <c r="D29" s="8">
-        <v>46157.771851261576</v>
+        <v>46157.60518459491</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>110</v>
@@ -3007,13 +3007,13 @@
         <v>112</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.781305798606</v>
+        <v>46073.61463913195</v>
       </c>
       <c r="C30" s="5">
-        <v>46157.771892199075</v>
+        <v>46157.6052255324</v>
       </c>
       <c r="D30" s="5">
-        <v>46157.771893240744</v>
+        <v>46157.60522657407</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -3068,13 +3068,13 @@
         <v>115</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.78130606482</v>
+        <v>46073.61463939815</v>
       </c>
       <c r="C31" s="8">
-        <v>46157.77191422453</v>
+        <v>46157.60524755787</v>
       </c>
       <c r="D31" s="8">
-        <v>46157.771915335645</v>
+        <v>46157.60524866898</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>116</v>
@@ -3129,13 +3129,13 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.78130635417</v>
+        <v>46073.6146396875</v>
       </c>
       <c r="C32" s="5">
-        <v>46113.537060428236</v>
+        <v>46113.37039376158</v>
       </c>
       <c r="D32" s="5">
-        <v>46113.537077800924</v>
+        <v>46113.37041113426</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3194,13 +3194,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.78130663194</v>
+        <v>46073.61463996528</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.53414924769</v>
+        <v>46097.367482581016</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.53415040509</v>
+        <v>46097.367483738424</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3255,13 +3255,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.7813069213</v>
+        <v>46073.61464025463</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.58889400463</v>
+        <v>46104.422227337964</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.58889570602</v>
+        <v>46104.42222903935</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3316,13 +3316,13 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.50065555556</v>
+        <v>46077.33398888889</v>
       </c>
       <c r="C35" s="8">
-        <v>46154.868248240746</v>
+        <v>46154.701581574074</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.66417827546</v>
+        <v>46181.497511608795</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3381,13 +3381,13 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.50123298611</v>
+        <v>46077.33456631945</v>
       </c>
       <c r="C36" s="5">
-        <v>46154.86742789352</v>
+        <v>46154.70076122685</v>
       </c>
       <c r="D36" s="5">
-        <v>46154.86742951389</v>
+        <v>46154.70076284722</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>80</v>
@@ -3436,13 +3436,13 @@
         <v>134</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.501358009264</v>
+        <v>46077.33469134259</v>
       </c>
       <c r="C37" s="8">
-        <v>46154.86796083333</v>
+        <v>46154.70129416666</v>
       </c>
       <c r="D37" s="8">
-        <v>46154.86796204861</v>
+        <v>46154.70129538194</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>135</v>
@@ -3491,13 +3491,13 @@
         <v>137</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.7813071875</v>
+        <v>46073.614640520835</v>
       </c>
       <c r="C38" s="5">
-        <v>46175.709567962964</v>
+        <v>46175.5429012963</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.66434030092</v>
+        <v>46181.49767363426</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>138</v>
@@ -3540,13 +3540,13 @@
         <v>140</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.781307488425</v>
+        <v>46073.61464082176</v>
       </c>
       <c r="C39" s="8">
-        <v>46098.51966484953</v>
+        <v>46098.35299818287</v>
       </c>
       <c r="D39" s="8">
-        <v>46098.51968671296</v>
+        <v>46098.3530200463</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>141</v>
@@ -3605,13 +3605,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.7813041551</v>
+        <v>46073.61463748843</v>
       </c>
       <c r="C40" s="5">
-        <v>46107.721847175926</v>
+        <v>46107.555180509255</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.66444446759</v>
+        <v>46181.49777780093</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -3670,13 +3670,13 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46092.504976909724</v>
+        <v>46092.33831024305</v>
       </c>
       <c r="C41" s="8">
-        <v>46107.722015983796</v>
+        <v>46107.55534931713</v>
       </c>
       <c r="D41" s="8">
-        <v>46107.7220319676</v>
+        <v>46107.55536530093</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3735,13 +3735,13 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46092.505018090276</v>
+        <v>46092.33835142361</v>
       </c>
       <c r="C42" s="5">
-        <v>46175.70954847222</v>
+        <v>46175.54288180555</v>
       </c>
       <c r="D42" s="5">
-        <v>46178.173813182875</v>
+        <v>46178.007146516204</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>153</v>
@@ -3800,13 +3800,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.78130445602</v>
+        <v>46073.61463778935</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.777069421296</v>
+        <v>46127.610402754624</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.664405868054</v>
+        <v>46181.49773920139</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3849,13 +3849,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.78130472222</v>
+        <v>46073.61463805556</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.64759277778</v>
+        <v>46127.48092611111</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.64790232639</v>
+        <v>46127.481235659725</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -3914,13 +3914,13 @@
         <v>166</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.781304965276</v>
+        <v>46073.61463829861</v>
       </c>
       <c r="C45" s="8">
-        <v>46127.777055</v>
+        <v>46127.610388333334</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.7770697338</v>
+        <v>46127.61040306713</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>167</v>
@@ -3979,13 +3979,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.781305185184</v>
+        <v>46073.61463851852</v>
       </c>
       <c r="C46" s="5">
-        <v>46157.765079687495</v>
+        <v>46157.59841302084</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.66456019676</v>
+        <v>46181.49789353009</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4028,13 +4028,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.78130541666</v>
+        <v>46073.614638750005</v>
       </c>
       <c r="C47" s="8">
-        <v>46128.49661835648</v>
+        <v>46128.32995168981</v>
       </c>
       <c r="D47" s="8">
-        <v>46128.496634826384</v>
+        <v>46128.32996815973</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>175</v>
@@ -4093,13 +4093,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.781305682875</v>
+        <v>46073.6146390162</v>
       </c>
       <c r="C48" s="5">
-        <v>46149.89362533565</v>
+        <v>46149.72695866898</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.66451681713</v>
+        <v>46181.49785015047</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4158,13 +4158,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.78130591435</v>
+        <v>46073.61463924768</v>
       </c>
       <c r="C49" s="8">
-        <v>46157.76442383102</v>
+        <v>46157.59775716435</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.66453760417</v>
+        <v>46181.4978709375</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4223,13 +4223,13 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.78130613426</v>
+        <v>46073.61463946759</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.77220969908</v>
+        <v>46157.605543032405</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.77227003472</v>
+        <v>46157.60560336805</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>159</v>
@@ -4272,13 +4272,13 @@
         <v>189</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.78130636574</v>
+        <v>46073.61463969907</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.7721819213</v>
+        <v>46157.60551525463</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.772197557875</v>
+        <v>46157.605530891204</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>190</v>
@@ -4337,13 +4337,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.78133149305</v>
+        <v>46073.61466482639</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.77218767361</v>
+        <v>46157.605521006946</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.77220337963</v>
+        <v>46157.60553671296</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4402,13 +4402,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.78133186343</v>
+        <v>46073.61466519676</v>
       </c>
       <c r="C53" s="8">
-        <v>46157.7721940162</v>
+        <v>46157.60552734954</v>
       </c>
       <c r="D53" s="8">
-        <v>46172.19673738426</v>
+        <v>46172.03007071759</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4467,13 +4467,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.50075619213</v>
+        <v>46077.334089525466</v>
       </c>
       <c r="C54" s="5">
-        <v>46157.76930983797</v>
+        <v>46157.602643171296</v>
       </c>
       <c r="D54" s="5">
-        <v>46157.7693262963</v>
+        <v>46157.60265962963</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4532,13 +4532,13 @@
         <v>201</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.78133226852</v>
+        <v>46073.61466560185</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.6295114699</v>
+        <v>46181.462844803245</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.664663495365</v>
+        <v>46181.49799682871</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>202</v>
@@ -4581,13 +4581,13 @@
         <v>204</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.78133261574</v>
+        <v>46073.61466594908</v>
       </c>
       <c r="C56" s="5">
-        <v>46148.43902174769</v>
+        <v>46148.27235508102</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.66481420139</v>
+        <v>46181.49814753472</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>205</v>
@@ -4646,13 +4646,13 @@
         <v>208</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.78133300926</v>
+        <v>46073.61466634259</v>
       </c>
       <c r="C57" s="8">
-        <v>46148.43903300926</v>
+        <v>46148.27236634259</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.6648505787</v>
+        <v>46181.49818391204</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>209</v>
@@ -4711,13 +4711,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.7813334838</v>
+        <v>46073.61466681713</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.62945255787</v>
+        <v>46181.4627858912</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.62946832176</v>
+        <v>46181.46280165509</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4776,13 +4776,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.78133387731</v>
+        <v>46073.61466721065</v>
       </c>
       <c r="C59" s="8">
-        <v>46181.62949673611</v>
+        <v>46181.462830069446</v>
       </c>
       <c r="D59" s="8">
-        <v>46181.629510729166</v>
+        <v>46181.462844062495</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4841,13 +4841,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.50297065973</v>
+        <v>46077.336303993055</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.629469594904</v>
+        <v>46181.46280292824</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.629485763886</v>
+        <v>46181.46281909722</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4906,13 +4906,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.781334224535</v>
+        <v>46073.61466755787</v>
       </c>
       <c r="C61" s="8">
-        <v>46148.43905277778</v>
+        <v>46148.272386111115</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.66493762731</v>
+        <v>46181.49827096065</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>156</v>
@@ -4969,13 +4969,13 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.78133457176</v>
+        <v>46073.614667905094</v>
       </c>
       <c r="C62" s="5">
-        <v>46148.439069305554</v>
+        <v>46148.27240263889</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.664980636575</v>
+        <v>46181.4983139699</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>157</v>
@@ -5034,13 +5034,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.78130702546</v>
+        <v>46073.61464035879</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.62877920139</v>
+        <v>46181.46211253472</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.66514677083</v>
+        <v>46181.49848010417</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5083,13 +5083,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.78130740741</v>
+        <v>46073.614640740736</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.628727337964</v>
+        <v>46181.4620606713</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.628744120375</v>
+        <v>46181.4620774537</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5148,13 +5148,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.78130768519</v>
+        <v>46073.61464101852</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.62861517361</v>
+        <v>46181.46194850694</v>
       </c>
       <c r="D65" s="8">
-        <v>46183.207376886574</v>
+        <v>46183.04071021991</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5213,13 +5213,13 @@
         <v>235</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.78130797454</v>
+        <v>46073.61464130787</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.628689502315</v>
+        <v>46181.46202283565</v>
       </c>
       <c r="D66" s="5">
-        <v>46183.20737744213</v>
+        <v>46183.04071077546</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>236</v>
@@ -5278,13 +5278,13 @@
         <v>238</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.78130825231</v>
+        <v>46073.61464158565</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.62876424768</v>
+        <v>46181.46209758102</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.179274062495</v>
+        <v>46184.01260739584</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>239</v>
@@ -5343,11 +5343,11 @@
         <v>241</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.78130855324</v>
+        <v>46073.614641886576</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46092.509188738426</v>
+        <v>46092.34252207176</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>242</v>
@@ -5390,11 +5390,11 @@
         <v>244</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.781308819445</v>
+        <v>46073.61464215278</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.12549048611</v>
+        <v>46194.95882381944</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>245</v>
@@ -5453,11 +5453,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.781309074075</v>
+        <v>46073.61464240741</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.12549313657</v>
+        <v>46194.95882646991</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>250</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="254">
   <si>
     <t>50001504 - ZITRON PERU CODESTABLE</t>
   </si>
@@ -439,19 +439,25 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1213381355319312</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1213381355319312</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
   </si>
   <si>
     <t>Planos preliminar,Planos motor proveedor</t>
@@ -1393,13 +1399,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.61463737268</v>
+        <v>46073.78130403935</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55695184028</v>
+        <v>46092.72361850695</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.65642046296</v>
+        <v>46112.823087129625</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1442,13 +1448,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.61463773148</v>
+        <v>46073.781304398144</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55691717593</v>
+        <v>46092.72358384259</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55695162037</v>
+        <v>46092.72361828704</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1507,13 +1513,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.61463802084</v>
+        <v>46073.7813046875</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.556917650465</v>
+        <v>46092.72358431713</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55695165509</v>
+        <v>46092.72361832176</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1572,13 +1578,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.61463835648</v>
+        <v>46073.78130502315</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55691803241</v>
+        <v>46092.72358469907</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55695146991</v>
+        <v>46092.72361813657</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1637,13 +1643,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.61463865741</v>
+        <v>46073.781305324075</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55691841435</v>
+        <v>46092.72358508102</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.52937359954</v>
+        <v>46100.69604026621</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1702,13 +1708,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.614638935185</v>
+        <v>46073.78130560185</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55691896991</v>
+        <v>46092.72358563657</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55695190972</v>
+        <v>46092.72361857639</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1767,13 +1773,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.61464047454</v>
+        <v>46073.7813071412</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.36058061343</v>
+        <v>46114.52724728009</v>
       </c>
       <c r="D10" s="5">
-        <v>46114.3605944213</v>
+        <v>46114.52726108796</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1820,13 +1826,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.61463789352</v>
+        <v>46073.78130456019</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.36049391204</v>
+        <v>46114.5271605787</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.36051359954</v>
+        <v>46114.5271802662</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1885,13 +1891,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.61463865741</v>
+        <v>46073.781305324075</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.36051849537</v>
+        <v>46114.527185162035</v>
       </c>
       <c r="D12" s="5">
-        <v>46114.36053143519</v>
+        <v>46114.52719810185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1950,13 +1956,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.61463895833</v>
+        <v>46073.781305625</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.36735673611</v>
+        <v>46097.53402340278</v>
       </c>
       <c r="D13" s="8">
-        <v>46097.36737695602</v>
+        <v>46097.53404362268</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -2015,13 +2021,13 @@
         <v>56</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.61463924768</v>
+        <v>46073.78130591435</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.360559837965</v>
+        <v>46114.52722650463</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.36058155092</v>
+        <v>46114.52724821759</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>57</v>
@@ -2080,13 +2086,13 @@
         <v>60</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.61463953704</v>
+        <v>46073.7813062037</v>
       </c>
       <c r="C15" s="8">
-        <v>46127.44410472222</v>
+        <v>46127.61077138889</v>
       </c>
       <c r="D15" s="8">
-        <v>46127.4441183912</v>
+        <v>46127.61078505787</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>61</v>
@@ -2133,13 +2139,13 @@
         <v>63</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.614640127314</v>
+        <v>46073.781306793986</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.36071721065</v>
+        <v>46114.527383877314</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.36073143518</v>
+        <v>46114.527398101854</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>64</v>
@@ -2198,13 +2204,13 @@
         <v>66</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.61463982639</v>
+        <v>46073.78130649305</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.360843194445</v>
+        <v>46114.52750986112</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.36085722222</v>
+        <v>46114.527523888886</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>67</v>
@@ -2263,13 +2269,13 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.614640694446</v>
+        <v>46073.78130736111</v>
       </c>
       <c r="C18" s="5">
-        <v>46127.44408350694</v>
+        <v>46127.61075017361</v>
       </c>
       <c r="D18" s="5">
-        <v>46127.44410570602</v>
+        <v>46127.61077237269</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -2328,13 +2334,13 @@
         <v>73</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.61463732639</v>
+        <v>46073.781303993055</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.367433287036</v>
+        <v>46097.5340999537</v>
       </c>
       <c r="D19" s="8">
-        <v>46100.54223155093</v>
+        <v>46100.70889821759</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>74</v>
@@ -2393,13 +2399,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.33391810185</v>
+        <v>46077.50058476852</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.36086756944</v>
+        <v>46114.52753423611</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.36088302083</v>
+        <v>46114.5275496875</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2458,13 +2464,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.61463765046</v>
+        <v>46073.78130431713</v>
       </c>
       <c r="C21" s="8">
-        <v>46169.65596876157</v>
+        <v>46169.82263542824</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.4976116551</v>
+        <v>46181.664278321754</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2507,13 +2513,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.61463792824</v>
+        <v>46073.78130459491</v>
       </c>
       <c r="C22" s="5">
-        <v>46157.604720104166</v>
+        <v>46157.77138677084</v>
       </c>
       <c r="D22" s="5">
-        <v>46157.6047322338</v>
+        <v>46157.77139890046</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2572,13 +2578,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.6146381713</v>
+        <v>46073.78130483796</v>
       </c>
       <c r="C23" s="8">
-        <v>46157.604641631944</v>
+        <v>46157.771308298616</v>
       </c>
       <c r="D23" s="8">
-        <v>46157.60464263889</v>
+        <v>46157.77130930556</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2633,13 +2639,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.61463840278</v>
+        <v>46073.781305069446</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.60470711805</v>
+        <v>46157.77137378472</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.60470844907</v>
+        <v>46157.77137511574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2694,13 +2700,13 @@
         <v>97</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.614639363426</v>
+        <v>46073.7813060301</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.604874675926</v>
+        <v>46157.77154134259</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.604885381945</v>
+        <v>46157.77155204861</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>
@@ -2759,13 +2765,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.61463960649</v>
+        <v>46073.781306273144</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.60482311343</v>
+        <v>46157.77148978009</v>
       </c>
       <c r="D26" s="5">
-        <v>46157.6048241088</v>
+        <v>46157.77149077546</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2820,13 +2826,13 @@
         <v>103</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.61463819444</v>
+        <v>46073.78130486111</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.60486304398</v>
+        <v>46157.77152971065</v>
       </c>
       <c r="D27" s="8">
-        <v>46157.60486414352</v>
+        <v>46157.77153081019</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>104</v>
@@ -2881,13 +2887,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.614638541665</v>
+        <v>46073.78130520834</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.60525976852</v>
+        <v>46157.77192643518</v>
       </c>
       <c r="D28" s="5">
-        <v>46170.01735829861</v>
+        <v>46170.184024965274</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -2946,13 +2952,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.61463885417</v>
+        <v>46073.78130552083</v>
       </c>
       <c r="C29" s="8">
-        <v>46157.60518351852</v>
+        <v>46157.771850185185</v>
       </c>
       <c r="D29" s="8">
-        <v>46157.60518459491</v>
+        <v>46157.771851261576</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>110</v>
@@ -3007,13 +3013,13 @@
         <v>112</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.61463913195</v>
+        <v>46073.781305798606</v>
       </c>
       <c r="C30" s="5">
-        <v>46157.6052255324</v>
+        <v>46157.771892199075</v>
       </c>
       <c r="D30" s="5">
-        <v>46157.60522657407</v>
+        <v>46157.771893240744</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -3068,13 +3074,13 @@
         <v>115</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.61463939815</v>
+        <v>46073.78130606482</v>
       </c>
       <c r="C31" s="8">
-        <v>46157.60524755787</v>
+        <v>46157.77191422453</v>
       </c>
       <c r="D31" s="8">
-        <v>46157.60524866898</v>
+        <v>46157.771915335645</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>116</v>
@@ -3129,13 +3135,13 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.6146396875</v>
+        <v>46073.78130635417</v>
       </c>
       <c r="C32" s="5">
-        <v>46113.37039376158</v>
+        <v>46113.537060428236</v>
       </c>
       <c r="D32" s="5">
-        <v>46113.37041113426</v>
+        <v>46113.537077800924</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3194,13 +3200,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.61463996528</v>
+        <v>46073.78130663194</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.367482581016</v>
+        <v>46097.53414924769</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.367483738424</v>
+        <v>46097.53415040509</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3255,13 +3261,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.61464025463</v>
+        <v>46073.7813069213</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.422227337964</v>
+        <v>46104.58889400463</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.42222903935</v>
+        <v>46104.58889570602</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3316,13 +3322,13 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.33398888889</v>
+        <v>46077.50065555556</v>
       </c>
       <c r="C35" s="8">
-        <v>46154.701581574074</v>
+        <v>46154.868248240746</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.497511608795</v>
+        <v>46181.66417827546</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3381,13 +3387,13 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.33456631945</v>
+        <v>46077.50123298611</v>
       </c>
       <c r="C36" s="5">
-        <v>46154.70076122685</v>
+        <v>46154.86742789352</v>
       </c>
       <c r="D36" s="5">
-        <v>46154.70076284722</v>
+        <v>46154.86742951389</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>80</v>
@@ -3436,13 +3442,13 @@
         <v>134</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.33469134259</v>
+        <v>46077.501358009264</v>
       </c>
       <c r="C37" s="8">
-        <v>46154.70129416666</v>
+        <v>46154.86796083333</v>
       </c>
       <c r="D37" s="8">
-        <v>46154.70129538194</v>
+        <v>46154.86796204861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>135</v>
@@ -3491,13 +3497,13 @@
         <v>137</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.614640520835</v>
+        <v>46073.7813071875</v>
       </c>
       <c r="C38" s="5">
-        <v>46175.5429012963</v>
+        <v>46175.709567962964</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.49767363426</v>
+        <v>46181.66434030092</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>138</v>
@@ -3540,13 +3546,13 @@
         <v>140</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.61464082176</v>
+        <v>46073.781307488425</v>
       </c>
       <c r="C39" s="8">
-        <v>46098.35299818287</v>
+        <v>46098.51966484953</v>
       </c>
       <c r="D39" s="8">
-        <v>46098.3530200463</v>
+        <v>46197.70883444445</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>141</v>
@@ -3605,13 +3611,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.61463748843</v>
+        <v>46073.7813041551</v>
       </c>
       <c r="C40" s="5">
-        <v>46107.555180509255</v>
+        <v>46107.721847175926</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.49777780093</v>
+        <v>46181.66444446759</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -3620,10 +3626,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46084</v>
@@ -3644,10 +3650,10 @@
         <v>138</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="5">
         <v>46084</v>
@@ -3667,28 +3673,28 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46092.33831024305</v>
+        <v>46092.504976909724</v>
       </c>
       <c r="C41" s="8">
-        <v>46107.55534931713</v>
+        <v>46107.722015983796</v>
       </c>
       <c r="D41" s="8">
-        <v>46107.55536530093</v>
+        <v>46107.7220319676</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I41" s="8">
         <v>46091</v>
@@ -3712,7 +3718,7 @@
         <v>146</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="8">
         <v>46091</v>
@@ -3732,28 +3738,28 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46092.33835142361</v>
+        <v>46092.505018090276</v>
       </c>
       <c r="C42" s="5">
-        <v>46175.54288180555</v>
+        <v>46175.70954847222</v>
       </c>
       <c r="D42" s="5">
-        <v>46178.007146516204</v>
+        <v>46178.173813182875</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46177</v>
@@ -3774,10 +3780,10 @@
         <v>138</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q42" s="5">
         <v>46177</v>
@@ -3797,19 +3803,19 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.61463778935</v>
+        <v>46073.78130445602</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.610402754624</v>
+        <v>46127.777069421296</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.49773920139</v>
+        <v>46181.664405868054</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>25</v>
@@ -3833,7 +3839,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3846,28 +3852,28 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.61463805556</v>
+        <v>46073.78130472222</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.48092611111</v>
+        <v>46127.64759277778</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.481235659725</v>
+        <v>46127.64790232639</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I44" s="5">
         <v>46085</v>
@@ -3885,13 +3891,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>127</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46085</v>
@@ -3911,28 +3917,28 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.61463829861</v>
+        <v>46073.781304965276</v>
       </c>
       <c r="C45" s="8">
-        <v>46127.610388333334</v>
+        <v>46127.777055</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.61040306713</v>
+        <v>46127.7770697338</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I45" s="8">
         <v>46087</v>
@@ -3950,13 +3956,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="8">
         <v>46087</v>
@@ -3976,19 +3982,19 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.61463851852</v>
+        <v>46073.781305185184</v>
       </c>
       <c r="C46" s="5">
-        <v>46157.59841302084</v>
+        <v>46157.765079687495</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.49789353009</v>
+        <v>46181.66456019676</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4012,7 +4018,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4025,28 +4031,28 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.614638750005</v>
+        <v>46073.78130541666</v>
       </c>
       <c r="C47" s="8">
-        <v>46128.32995168981</v>
+        <v>46128.49661835648</v>
       </c>
       <c r="D47" s="8">
-        <v>46128.32996815973</v>
+        <v>46128.496634826384</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I47" s="8">
         <v>46091</v>
@@ -4064,13 +4070,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q47" s="8">
         <v>46091</v>
@@ -4090,28 +4096,28 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B48" s="5">
+        <v>46073.781305682875</v>
+      </c>
+      <c r="C48" s="5">
+        <v>46149.89362533565</v>
+      </c>
+      <c r="D48" s="5">
+        <v>46181.66451681713</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="B48" s="5">
-        <v>46073.6146390162</v>
-      </c>
-      <c r="C48" s="5">
-        <v>46149.72695866898</v>
-      </c>
-      <c r="D48" s="5">
-        <v>46181.49785015047</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46100</v>
@@ -4129,13 +4135,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q48" s="5">
         <v>46100</v>
@@ -4155,28 +4161,28 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.61463924768</v>
+        <v>46073.78130591435</v>
       </c>
       <c r="C49" s="8">
-        <v>46157.59775716435</v>
+        <v>46157.76442383102</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.4978709375</v>
+        <v>46181.66453760417</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I49" s="8">
         <v>46120</v>
@@ -4194,13 +4200,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q49" s="8">
         <v>46120</v>
@@ -4220,19 +4226,19 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.61463946759</v>
+        <v>46073.78130613426</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.605543032405</v>
+        <v>46157.77220969908</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.60560336805</v>
+        <v>46157.77227003472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4256,7 +4262,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4269,28 +4275,28 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.61463969907</v>
+        <v>46073.78130636574</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.60551525463</v>
+        <v>46157.7721819213</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.605530891204</v>
+        <v>46157.772197557875</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I51" s="8">
         <v>46087</v>
@@ -4308,13 +4314,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>104</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="8">
         <v>46087</v>
@@ -4334,28 +4340,28 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.61466482639</v>
+        <v>46073.78133149305</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.605521006946</v>
+        <v>46157.77218767361</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.60553671296</v>
+        <v>46157.77220337963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I52" s="5">
         <v>46150</v>
@@ -4373,13 +4379,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="5">
         <v>46150</v>
@@ -4399,28 +4405,28 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.61466519676</v>
+        <v>46073.78133186343</v>
       </c>
       <c r="C53" s="8">
-        <v>46157.60552734954</v>
+        <v>46157.7721940162</v>
       </c>
       <c r="D53" s="8">
-        <v>46172.03007071759</v>
+        <v>46172.19673738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I53" s="8">
         <v>46170</v>
@@ -4438,13 +4444,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>113</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q53" s="8">
         <v>46170</v>
@@ -4464,28 +4470,28 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.334089525466</v>
+        <v>46077.50075619213</v>
       </c>
       <c r="C54" s="5">
-        <v>46157.602643171296</v>
+        <v>46157.76930983797</v>
       </c>
       <c r="D54" s="5">
-        <v>46157.60265962963</v>
+        <v>46157.7693262963</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I54" s="5">
         <v>46154</v>
@@ -4503,13 +4509,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46154</v>
@@ -4529,19 +4535,19 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.61466560185</v>
+        <v>46073.78133226852</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.462844803245</v>
+        <v>46181.6295114699</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.49799682871</v>
+        <v>46181.664663495365</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4565,7 +4571,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4578,19 +4584,19 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.61466594908</v>
+        <v>46073.78133261574</v>
       </c>
       <c r="C56" s="5">
-        <v>46148.27235508102</v>
+        <v>46148.43902174769</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.49814753472</v>
+        <v>46181.66481420139</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4617,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q56" s="5">
         <v>46122</v>
@@ -4632,7 +4638,7 @@
         <v>46141</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4643,19 +4649,19 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.61466634259</v>
+        <v>46073.78133300926</v>
       </c>
       <c r="C57" s="8">
-        <v>46148.27236634259</v>
+        <v>46148.43903300926</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.49818391204</v>
+        <v>46181.6648505787</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -4682,13 +4688,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="8">
         <v>46174</v>
@@ -4708,19 +4714,19 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.61466681713</v>
+        <v>46073.7813334838</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.4627858912</v>
+        <v>46181.62945255787</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.46280165509</v>
+        <v>46181.62946832176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4747,13 +4753,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="5">
         <v>46154</v>
@@ -4773,19 +4779,19 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.61466721065</v>
+        <v>46073.78133387731</v>
       </c>
       <c r="C59" s="8">
-        <v>46181.462830069446</v>
+        <v>46181.62949673611</v>
       </c>
       <c r="D59" s="8">
-        <v>46181.462844062495</v>
+        <v>46181.629510729166</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4812,13 +4818,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="8">
         <v>46156</v>
@@ -4838,19 +4844,19 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.336303993055</v>
+        <v>46077.50297065973</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.46280292824</v>
+        <v>46181.629469594904</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.46281909722</v>
+        <v>46181.629485763886</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4877,13 +4883,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="5">
         <v>46160</v>
@@ -4903,19 +4909,19 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.61466755787</v>
+        <v>46073.781334224535</v>
       </c>
       <c r="C61" s="8">
-        <v>46148.272386111115</v>
+        <v>46148.43905277778</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.49827096065</v>
+        <v>46181.66493762731</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -4940,13 +4946,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q61" s="8">
         <v>46176</v>
@@ -4966,19 +4972,19 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.614667905094</v>
+        <v>46073.78133457176</v>
       </c>
       <c r="C62" s="5">
-        <v>46148.27240263889</v>
+        <v>46148.439069305554</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.4983139699</v>
+        <v>46181.664980636575</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5005,13 +5011,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q62" s="5">
         <v>46178</v>
@@ -5031,19 +5037,19 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.61464035879</v>
+        <v>46073.78130702546</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.46211253472</v>
+        <v>46181.62877920139</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.49848010417</v>
+        <v>46181.66514677083</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5067,7 +5073,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5080,19 +5086,19 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.614640740736</v>
+        <v>46073.78130740741</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.4620606713</v>
+        <v>46181.628727337964</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.4620774537</v>
+        <v>46181.628744120375</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5119,13 +5125,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46178</v>
@@ -5145,19 +5151,19 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.61464101852</v>
+        <v>46073.78130768519</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.46194850694</v>
+        <v>46181.62861517361</v>
       </c>
       <c r="D65" s="8">
-        <v>46183.04071021991</v>
+        <v>46183.207376886574</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5184,13 +5190,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q65" s="8">
         <v>46181</v>
@@ -5210,28 +5216,28 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.61464130787</v>
+        <v>46073.78130797454</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.46202283565</v>
+        <v>46181.628689502315</v>
       </c>
       <c r="D66" s="5">
-        <v>46183.04071077546</v>
+        <v>46183.20737744213</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5249,13 +5255,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -5275,28 +5281,28 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.61464158565</v>
+        <v>46073.78130825231</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.46209758102</v>
+        <v>46181.62876424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.01260739584</v>
+        <v>46184.179274062495</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I67" s="8">
         <v>46184</v>
@@ -5314,13 +5320,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q67" s="8">
         <v>46183</v>
@@ -5340,17 +5346,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.614641886576</v>
+        <v>46073.78130855324</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46092.34252207176</v>
+        <v>46092.509188738426</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5374,7 +5380,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5387,26 +5393,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.61464215278</v>
+        <v>46073.781308819445</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46194.95882381944</v>
+        <v>46195.12549048611</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I69" s="8">
         <v>46185</v>
@@ -5424,13 +5430,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q69" s="8">
         <v>46184</v>
@@ -5445,31 +5451,31 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.61464240741</v>
+        <v>46073.781309074075</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46194.95882646991</v>
+        <v>46195.12549313657</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I70" s="5">
         <v>46185</v>
@@ -5487,13 +5493,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q70" s="5">
         <v>46184</v>
@@ -5508,7 +5514,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -1399,13 +1399,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.78130403935</v>
+        <v>46073.61463737268</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72361850695</v>
+        <v>46092.55695184028</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.823087129625</v>
+        <v>46112.65642046296</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1448,13 +1448,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.781304398144</v>
+        <v>46073.61463773148</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72358384259</v>
+        <v>46092.55691717593</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72361828704</v>
+        <v>46092.55695162037</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1513,13 +1513,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.7813046875</v>
+        <v>46073.61463802084</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72358431713</v>
+        <v>46092.556917650465</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72361832176</v>
+        <v>46092.55695165509</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1578,13 +1578,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.78130502315</v>
+        <v>46073.61463835648</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72358469907</v>
+        <v>46092.55691803241</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72361813657</v>
+        <v>46092.55695146991</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1643,13 +1643,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.781305324075</v>
+        <v>46073.61463865741</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72358508102</v>
+        <v>46092.55691841435</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.69604026621</v>
+        <v>46100.52937359954</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1708,13 +1708,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.78130560185</v>
+        <v>46073.614638935185</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72358563657</v>
+        <v>46092.55691896991</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72361857639</v>
+        <v>46092.55695190972</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1773,13 +1773,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.7813071412</v>
+        <v>46073.61464047454</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.52724728009</v>
+        <v>46114.36058061343</v>
       </c>
       <c r="D10" s="5">
-        <v>46114.52726108796</v>
+        <v>46114.3605944213</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1826,13 +1826,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.78130456019</v>
+        <v>46073.61463789352</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.5271605787</v>
+        <v>46114.36049391204</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.5271802662</v>
+        <v>46114.36051359954</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1891,13 +1891,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.781305324075</v>
+        <v>46073.61463865741</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.527185162035</v>
+        <v>46114.36051849537</v>
       </c>
       <c r="D12" s="5">
-        <v>46114.52719810185</v>
+        <v>46114.36053143519</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1956,13 +1956,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.781305625</v>
+        <v>46073.61463895833</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.53402340278</v>
+        <v>46097.36735673611</v>
       </c>
       <c r="D13" s="8">
-        <v>46097.53404362268</v>
+        <v>46097.36737695602</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -2021,13 +2021,13 @@
         <v>56</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.78130591435</v>
+        <v>46073.61463924768</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.52722650463</v>
+        <v>46114.360559837965</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.52724821759</v>
+        <v>46114.36058155092</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>57</v>
@@ -2086,13 +2086,13 @@
         <v>60</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.7813062037</v>
+        <v>46073.61463953704</v>
       </c>
       <c r="C15" s="8">
-        <v>46127.61077138889</v>
+        <v>46127.44410472222</v>
       </c>
       <c r="D15" s="8">
-        <v>46127.61078505787</v>
+        <v>46127.4441183912</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>61</v>
@@ -2139,13 +2139,13 @@
         <v>63</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.781306793986</v>
+        <v>46073.614640127314</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.527383877314</v>
+        <v>46114.36071721065</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.527398101854</v>
+        <v>46114.36073143518</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>64</v>
@@ -2204,13 +2204,13 @@
         <v>66</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.78130649305</v>
+        <v>46073.61463982639</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.52750986112</v>
+        <v>46114.360843194445</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.527523888886</v>
+        <v>46114.36085722222</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>67</v>
@@ -2269,13 +2269,13 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.78130736111</v>
+        <v>46073.614640694446</v>
       </c>
       <c r="C18" s="5">
-        <v>46127.61075017361</v>
+        <v>46127.44408350694</v>
       </c>
       <c r="D18" s="5">
-        <v>46127.61077237269</v>
+        <v>46127.44410570602</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -2334,13 +2334,13 @@
         <v>73</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.781303993055</v>
+        <v>46073.61463732639</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.5340999537</v>
+        <v>46097.367433287036</v>
       </c>
       <c r="D19" s="8">
-        <v>46100.70889821759</v>
+        <v>46100.54223155093</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>74</v>
@@ -2399,13 +2399,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.50058476852</v>
+        <v>46077.33391810185</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.52753423611</v>
+        <v>46114.36086756944</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.5275496875</v>
+        <v>46114.36088302083</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2464,13 +2464,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.78130431713</v>
+        <v>46073.61463765046</v>
       </c>
       <c r="C21" s="8">
-        <v>46169.82263542824</v>
+        <v>46169.65596876157</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.664278321754</v>
+        <v>46181.4976116551</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2513,13 +2513,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.78130459491</v>
+        <v>46073.61463792824</v>
       </c>
       <c r="C22" s="5">
-        <v>46157.77138677084</v>
+        <v>46157.604720104166</v>
       </c>
       <c r="D22" s="5">
-        <v>46157.77139890046</v>
+        <v>46157.6047322338</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2578,13 +2578,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.78130483796</v>
+        <v>46073.6146381713</v>
       </c>
       <c r="C23" s="8">
-        <v>46157.771308298616</v>
+        <v>46157.604641631944</v>
       </c>
       <c r="D23" s="8">
-        <v>46157.77130930556</v>
+        <v>46157.60464263889</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2639,13 +2639,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.781305069446</v>
+        <v>46073.61463840278</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.77137378472</v>
+        <v>46157.60470711805</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.77137511574</v>
+        <v>46157.60470844907</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2700,13 +2700,13 @@
         <v>97</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.7813060301</v>
+        <v>46073.614639363426</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.77154134259</v>
+        <v>46157.604874675926</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.77155204861</v>
+        <v>46157.604885381945</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>
@@ -2765,13 +2765,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.781306273144</v>
+        <v>46073.61463960649</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.77148978009</v>
+        <v>46157.60482311343</v>
       </c>
       <c r="D26" s="5">
-        <v>46157.77149077546</v>
+        <v>46157.6048241088</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2826,13 +2826,13 @@
         <v>103</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.78130486111</v>
+        <v>46073.61463819444</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.77152971065</v>
+        <v>46157.60486304398</v>
       </c>
       <c r="D27" s="8">
-        <v>46157.77153081019</v>
+        <v>46157.60486414352</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>104</v>
@@ -2887,13 +2887,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.78130520834</v>
+        <v>46073.614638541665</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.77192643518</v>
+        <v>46157.60525976852</v>
       </c>
       <c r="D28" s="5">
-        <v>46170.184024965274</v>
+        <v>46170.01735829861</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -2952,13 +2952,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.78130552083</v>
+        <v>46073.61463885417</v>
       </c>
       <c r="C29" s="8">
-        <v>46157.771850185185</v>
+        <v>46157.60518351852</v>
       </c>
       <c r="D29" s="8">
-        <v>46157.771851261576</v>
+        <v>46157.60518459491</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>110</v>
@@ -3013,13 +3013,13 @@
         <v>112</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.781305798606</v>
+        <v>46073.61463913195</v>
       </c>
       <c r="C30" s="5">
-        <v>46157.771892199075</v>
+        <v>46157.6052255324</v>
       </c>
       <c r="D30" s="5">
-        <v>46157.771893240744</v>
+        <v>46157.60522657407</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -3074,13 +3074,13 @@
         <v>115</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.78130606482</v>
+        <v>46073.61463939815</v>
       </c>
       <c r="C31" s="8">
-        <v>46157.77191422453</v>
+        <v>46157.60524755787</v>
       </c>
       <c r="D31" s="8">
-        <v>46157.771915335645</v>
+        <v>46157.60524866898</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>116</v>
@@ -3135,13 +3135,13 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.78130635417</v>
+        <v>46073.6146396875</v>
       </c>
       <c r="C32" s="5">
-        <v>46113.537060428236</v>
+        <v>46113.37039376158</v>
       </c>
       <c r="D32" s="5">
-        <v>46113.537077800924</v>
+        <v>46113.37041113426</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3200,13 +3200,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.78130663194</v>
+        <v>46073.61463996528</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.53414924769</v>
+        <v>46097.367482581016</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.53415040509</v>
+        <v>46097.367483738424</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3261,13 +3261,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.7813069213</v>
+        <v>46073.61464025463</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.58889400463</v>
+        <v>46104.422227337964</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.58889570602</v>
+        <v>46104.42222903935</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3322,13 +3322,13 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.50065555556</v>
+        <v>46077.33398888889</v>
       </c>
       <c r="C35" s="8">
-        <v>46154.868248240746</v>
+        <v>46154.701581574074</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.66417827546</v>
+        <v>46181.497511608795</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3387,13 +3387,13 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.50123298611</v>
+        <v>46077.33456631945</v>
       </c>
       <c r="C36" s="5">
-        <v>46154.86742789352</v>
+        <v>46154.70076122685</v>
       </c>
       <c r="D36" s="5">
-        <v>46154.86742951389</v>
+        <v>46154.70076284722</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>80</v>
@@ -3442,13 +3442,13 @@
         <v>134</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.501358009264</v>
+        <v>46077.33469134259</v>
       </c>
       <c r="C37" s="8">
-        <v>46154.86796083333</v>
+        <v>46154.70129416666</v>
       </c>
       <c r="D37" s="8">
-        <v>46154.86796204861</v>
+        <v>46154.70129538194</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>135</v>
@@ -3497,13 +3497,13 @@
         <v>137</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.7813071875</v>
+        <v>46073.614640520835</v>
       </c>
       <c r="C38" s="5">
-        <v>46175.709567962964</v>
+        <v>46175.5429012963</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.66434030092</v>
+        <v>46181.49767363426</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>138</v>
@@ -3546,13 +3546,13 @@
         <v>140</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.781307488425</v>
+        <v>46073.61464082176</v>
       </c>
       <c r="C39" s="8">
-        <v>46098.51966484953</v>
+        <v>46098.35299818287</v>
       </c>
       <c r="D39" s="8">
-        <v>46197.70883444445</v>
+        <v>46197.54216777778</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>141</v>
@@ -3611,13 +3611,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.7813041551</v>
+        <v>46073.61463748843</v>
       </c>
       <c r="C40" s="5">
-        <v>46107.721847175926</v>
+        <v>46107.555180509255</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.66444446759</v>
+        <v>46181.49777780093</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -3676,13 +3676,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46092.504976909724</v>
+        <v>46092.33831024305</v>
       </c>
       <c r="C41" s="8">
-        <v>46107.722015983796</v>
+        <v>46107.55534931713</v>
       </c>
       <c r="D41" s="8">
-        <v>46107.7220319676</v>
+        <v>46107.55536530093</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3741,13 +3741,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46092.505018090276</v>
+        <v>46092.33835142361</v>
       </c>
       <c r="C42" s="5">
-        <v>46175.70954847222</v>
+        <v>46175.54288180555</v>
       </c>
       <c r="D42" s="5">
-        <v>46178.173813182875</v>
+        <v>46178.007146516204</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3806,13 +3806,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.78130445602</v>
+        <v>46073.61463778935</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.777069421296</v>
+        <v>46127.610402754624</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.664405868054</v>
+        <v>46181.49773920139</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3855,13 +3855,13 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.78130472222</v>
+        <v>46073.61463805556</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.64759277778</v>
+        <v>46127.48092611111</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.64790232639</v>
+        <v>46127.481235659725</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -3920,13 +3920,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.781304965276</v>
+        <v>46073.61463829861</v>
       </c>
       <c r="C45" s="8">
-        <v>46127.777055</v>
+        <v>46127.610388333334</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.7770697338</v>
+        <v>46127.61040306713</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -3985,13 +3985,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.781305185184</v>
+        <v>46073.61463851852</v>
       </c>
       <c r="C46" s="5">
-        <v>46157.765079687495</v>
+        <v>46157.59841302084</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.66456019676</v>
+        <v>46181.49789353009</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -4034,13 +4034,13 @@
         <v>176</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.78130541666</v>
+        <v>46073.614638750005</v>
       </c>
       <c r="C47" s="8">
-        <v>46128.49661835648</v>
+        <v>46128.32995168981</v>
       </c>
       <c r="D47" s="8">
-        <v>46128.496634826384</v>
+        <v>46128.32996815973</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>177</v>
@@ -4099,13 +4099,13 @@
         <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.781305682875</v>
+        <v>46073.6146390162</v>
       </c>
       <c r="C48" s="5">
-        <v>46149.89362533565</v>
+        <v>46149.72695866898</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.66451681713</v>
+        <v>46181.49785015047</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>182</v>
@@ -4164,13 +4164,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.78130591435</v>
+        <v>46073.61463924768</v>
       </c>
       <c r="C49" s="8">
-        <v>46157.76442383102</v>
+        <v>46157.59775716435</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.66453760417</v>
+        <v>46181.4978709375</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4229,13 +4229,13 @@
         <v>189</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.78130613426</v>
+        <v>46073.61463946759</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.77220969908</v>
+        <v>46157.605543032405</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.77227003472</v>
+        <v>46157.60560336805</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>161</v>
@@ -4278,13 +4278,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.78130636574</v>
+        <v>46073.61463969907</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.7721819213</v>
+        <v>46157.60551525463</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.772197557875</v>
+        <v>46157.605530891204</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4343,13 +4343,13 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.78133149305</v>
+        <v>46073.61466482639</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.77218767361</v>
+        <v>46157.605521006946</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.77220337963</v>
+        <v>46157.60553671296</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4408,13 +4408,13 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.78133186343</v>
+        <v>46073.61466519676</v>
       </c>
       <c r="C53" s="8">
-        <v>46157.7721940162</v>
+        <v>46157.60552734954</v>
       </c>
       <c r="D53" s="8">
-        <v>46172.19673738426</v>
+        <v>46172.03007071759</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4473,13 +4473,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.50075619213</v>
+        <v>46077.334089525466</v>
       </c>
       <c r="C54" s="5">
-        <v>46157.76930983797</v>
+        <v>46157.602643171296</v>
       </c>
       <c r="D54" s="5">
-        <v>46157.7693262963</v>
+        <v>46157.60265962963</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4538,13 +4538,13 @@
         <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.78133226852</v>
+        <v>46073.61466560185</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.6295114699</v>
+        <v>46181.462844803245</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.664663495365</v>
+        <v>46181.49799682871</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4587,13 +4587,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.78133261574</v>
+        <v>46073.61466594908</v>
       </c>
       <c r="C56" s="5">
-        <v>46148.43902174769</v>
+        <v>46148.27235508102</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.66481420139</v>
+        <v>46181.49814753472</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4652,13 +4652,13 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.78133300926</v>
+        <v>46073.61466634259</v>
       </c>
       <c r="C57" s="8">
-        <v>46148.43903300926</v>
+        <v>46148.27236634259</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.6648505787</v>
+        <v>46181.49818391204</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>211</v>
@@ -4717,13 +4717,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.7813334838</v>
+        <v>46073.61466681713</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.62945255787</v>
+        <v>46181.4627858912</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.62946832176</v>
+        <v>46181.46280165509</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4782,13 +4782,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.78133387731</v>
+        <v>46073.61466721065</v>
       </c>
       <c r="C59" s="8">
-        <v>46181.62949673611</v>
+        <v>46181.462830069446</v>
       </c>
       <c r="D59" s="8">
-        <v>46181.629510729166</v>
+        <v>46181.462844062495</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4847,13 +4847,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.50297065973</v>
+        <v>46077.336303993055</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.629469594904</v>
+        <v>46181.46280292824</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.629485763886</v>
+        <v>46181.46281909722</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4912,13 +4912,13 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.781334224535</v>
+        <v>46073.61466755787</v>
       </c>
       <c r="C61" s="8">
-        <v>46148.43905277778</v>
+        <v>46148.272386111115</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.66493762731</v>
+        <v>46181.49827096065</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>158</v>
@@ -4975,13 +4975,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.78133457176</v>
+        <v>46073.614667905094</v>
       </c>
       <c r="C62" s="5">
-        <v>46148.439069305554</v>
+        <v>46148.27240263889</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.664980636575</v>
+        <v>46181.4983139699</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>159</v>
@@ -5040,13 +5040,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.78130702546</v>
+        <v>46073.61464035879</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.62877920139</v>
+        <v>46181.46211253472</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.66514677083</v>
+        <v>46181.49848010417</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5089,13 +5089,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.78130740741</v>
+        <v>46073.614640740736</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.628727337964</v>
+        <v>46181.4620606713</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.628744120375</v>
+        <v>46181.4620774537</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5154,13 +5154,13 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.78130768519</v>
+        <v>46073.61464101852</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.62861517361</v>
+        <v>46181.46194850694</v>
       </c>
       <c r="D65" s="8">
-        <v>46183.207376886574</v>
+        <v>46183.04071021991</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5219,13 +5219,13 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.78130797454</v>
+        <v>46073.61464130787</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.628689502315</v>
+        <v>46181.46202283565</v>
       </c>
       <c r="D66" s="5">
-        <v>46183.20737744213</v>
+        <v>46183.04071077546</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>238</v>
@@ -5284,13 +5284,13 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.78130825231</v>
+        <v>46073.61464158565</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.62876424768</v>
+        <v>46181.46209758102</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.179274062495</v>
+        <v>46184.01260739584</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5349,11 +5349,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.78130855324</v>
+        <v>46073.614641886576</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46092.509188738426</v>
+        <v>46092.34252207176</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5396,11 +5396,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.781308819445</v>
+        <v>46073.61464215278</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.12549048611</v>
+        <v>46194.95882381944</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>247</v>
@@ -5459,11 +5459,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.781309074075</v>
+        <v>46073.61464240741</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.12549313657</v>
+        <v>46194.95882646991</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>252</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -1399,13 +1399,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.61463737268</v>
+        <v>46073.78130403935</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55695184028</v>
+        <v>46092.72361850695</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.65642046296</v>
+        <v>46112.823087129625</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1448,13 +1448,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.61463773148</v>
+        <v>46073.781304398144</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55691717593</v>
+        <v>46092.72358384259</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55695162037</v>
+        <v>46092.72361828704</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1513,13 +1513,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.61463802084</v>
+        <v>46073.7813046875</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.556917650465</v>
+        <v>46092.72358431713</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55695165509</v>
+        <v>46092.72361832176</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1578,13 +1578,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.61463835648</v>
+        <v>46073.78130502315</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55691803241</v>
+        <v>46092.72358469907</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55695146991</v>
+        <v>46092.72361813657</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1643,13 +1643,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.61463865741</v>
+        <v>46073.781305324075</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55691841435</v>
+        <v>46092.72358508102</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.52937359954</v>
+        <v>46100.69604026621</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1708,13 +1708,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.614638935185</v>
+        <v>46073.78130560185</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55691896991</v>
+        <v>46092.72358563657</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55695190972</v>
+        <v>46092.72361857639</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1773,13 +1773,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.61464047454</v>
+        <v>46073.7813071412</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.36058061343</v>
+        <v>46114.52724728009</v>
       </c>
       <c r="D10" s="5">
-        <v>46114.3605944213</v>
+        <v>46114.52726108796</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1826,13 +1826,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.61463789352</v>
+        <v>46073.78130456019</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.36049391204</v>
+        <v>46114.5271605787</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.36051359954</v>
+        <v>46114.5271802662</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1891,13 +1891,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.61463865741</v>
+        <v>46073.781305324075</v>
       </c>
       <c r="C12" s="5">
-        <v>46114.36051849537</v>
+        <v>46114.527185162035</v>
       </c>
       <c r="D12" s="5">
-        <v>46114.36053143519</v>
+        <v>46114.52719810185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -1956,13 +1956,13 @@
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.61463895833</v>
+        <v>46073.781305625</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.36735673611</v>
+        <v>46097.53402340278</v>
       </c>
       <c r="D13" s="8">
-        <v>46097.36737695602</v>
+        <v>46097.53404362268</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>54</v>
@@ -2021,13 +2021,13 @@
         <v>56</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.61463924768</v>
+        <v>46073.78130591435</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.360559837965</v>
+        <v>46114.52722650463</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.36058155092</v>
+        <v>46114.52724821759</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>57</v>
@@ -2086,13 +2086,13 @@
         <v>60</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.61463953704</v>
+        <v>46073.7813062037</v>
       </c>
       <c r="C15" s="8">
-        <v>46127.44410472222</v>
+        <v>46127.61077138889</v>
       </c>
       <c r="D15" s="8">
-        <v>46127.4441183912</v>
+        <v>46127.61078505787</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>61</v>
@@ -2139,13 +2139,13 @@
         <v>63</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.614640127314</v>
+        <v>46073.781306793986</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.36071721065</v>
+        <v>46114.527383877314</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.36073143518</v>
+        <v>46114.527398101854</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>64</v>
@@ -2204,13 +2204,13 @@
         <v>66</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.61463982639</v>
+        <v>46073.78130649305</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.360843194445</v>
+        <v>46114.52750986112</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.36085722222</v>
+        <v>46114.527523888886</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>67</v>
@@ -2269,13 +2269,13 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.614640694446</v>
+        <v>46073.78130736111</v>
       </c>
       <c r="C18" s="5">
-        <v>46127.44408350694</v>
+        <v>46127.61075017361</v>
       </c>
       <c r="D18" s="5">
-        <v>46127.44410570602</v>
+        <v>46127.61077237269</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -2334,13 +2334,13 @@
         <v>73</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.61463732639</v>
+        <v>46073.781303993055</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.367433287036</v>
+        <v>46097.5340999537</v>
       </c>
       <c r="D19" s="8">
-        <v>46100.54223155093</v>
+        <v>46100.70889821759</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>74</v>
@@ -2399,13 +2399,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.33391810185</v>
+        <v>46077.50058476852</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.36086756944</v>
+        <v>46114.52753423611</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.36088302083</v>
+        <v>46114.5275496875</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2464,13 +2464,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.61463765046</v>
+        <v>46073.78130431713</v>
       </c>
       <c r="C21" s="8">
-        <v>46169.65596876157</v>
+        <v>46169.82263542824</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.4976116551</v>
+        <v>46181.664278321754</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2513,13 +2513,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.61463792824</v>
+        <v>46073.78130459491</v>
       </c>
       <c r="C22" s="5">
-        <v>46157.604720104166</v>
+        <v>46157.77138677084</v>
       </c>
       <c r="D22" s="5">
-        <v>46157.6047322338</v>
+        <v>46157.77139890046</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2578,13 +2578,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.6146381713</v>
+        <v>46073.78130483796</v>
       </c>
       <c r="C23" s="8">
-        <v>46157.604641631944</v>
+        <v>46157.771308298616</v>
       </c>
       <c r="D23" s="8">
-        <v>46157.60464263889</v>
+        <v>46157.77130930556</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2639,13 +2639,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.61463840278</v>
+        <v>46073.781305069446</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.60470711805</v>
+        <v>46157.77137378472</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.60470844907</v>
+        <v>46157.77137511574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2700,13 +2700,13 @@
         <v>97</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.614639363426</v>
+        <v>46073.7813060301</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.604874675926</v>
+        <v>46157.77154134259</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.604885381945</v>
+        <v>46157.77155204861</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>
@@ -2765,13 +2765,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.61463960649</v>
+        <v>46073.781306273144</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.60482311343</v>
+        <v>46157.77148978009</v>
       </c>
       <c r="D26" s="5">
-        <v>46157.6048241088</v>
+        <v>46157.77149077546</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2826,13 +2826,13 @@
         <v>103</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.61463819444</v>
+        <v>46073.78130486111</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.60486304398</v>
+        <v>46157.77152971065</v>
       </c>
       <c r="D27" s="8">
-        <v>46157.60486414352</v>
+        <v>46157.77153081019</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>104</v>
@@ -2887,13 +2887,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.614638541665</v>
+        <v>46073.78130520834</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.60525976852</v>
+        <v>46157.77192643518</v>
       </c>
       <c r="D28" s="5">
-        <v>46170.01735829861</v>
+        <v>46170.184024965274</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -2952,13 +2952,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.61463885417</v>
+        <v>46073.78130552083</v>
       </c>
       <c r="C29" s="8">
-        <v>46157.60518351852</v>
+        <v>46157.771850185185</v>
       </c>
       <c r="D29" s="8">
-        <v>46157.60518459491</v>
+        <v>46157.771851261576</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>110</v>
@@ -3013,13 +3013,13 @@
         <v>112</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.61463913195</v>
+        <v>46073.781305798606</v>
       </c>
       <c r="C30" s="5">
-        <v>46157.6052255324</v>
+        <v>46157.771892199075</v>
       </c>
       <c r="D30" s="5">
-        <v>46157.60522657407</v>
+        <v>46157.771893240744</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -3074,13 +3074,13 @@
         <v>115</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.61463939815</v>
+        <v>46073.78130606482</v>
       </c>
       <c r="C31" s="8">
-        <v>46157.60524755787</v>
+        <v>46157.77191422453</v>
       </c>
       <c r="D31" s="8">
-        <v>46157.60524866898</v>
+        <v>46157.771915335645</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>116</v>
@@ -3135,13 +3135,13 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.6146396875</v>
+        <v>46073.78130635417</v>
       </c>
       <c r="C32" s="5">
-        <v>46113.37039376158</v>
+        <v>46113.537060428236</v>
       </c>
       <c r="D32" s="5">
-        <v>46113.37041113426</v>
+        <v>46113.537077800924</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -3200,13 +3200,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.61463996528</v>
+        <v>46073.78130663194</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.367482581016</v>
+        <v>46097.53414924769</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.367483738424</v>
+        <v>46097.53415040509</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3261,13 +3261,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.61464025463</v>
+        <v>46073.7813069213</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.422227337964</v>
+        <v>46104.58889400463</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.42222903935</v>
+        <v>46104.58889570602</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3322,13 +3322,13 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.33398888889</v>
+        <v>46077.50065555556</v>
       </c>
       <c r="C35" s="8">
-        <v>46154.701581574074</v>
+        <v>46154.868248240746</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.497511608795</v>
+        <v>46181.66417827546</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3387,13 +3387,13 @@
         <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.33456631945</v>
+        <v>46077.50123298611</v>
       </c>
       <c r="C36" s="5">
-        <v>46154.70076122685</v>
+        <v>46154.86742789352</v>
       </c>
       <c r="D36" s="5">
-        <v>46154.70076284722</v>
+        <v>46154.86742951389</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>80</v>
@@ -3442,13 +3442,13 @@
         <v>134</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.33469134259</v>
+        <v>46077.501358009264</v>
       </c>
       <c r="C37" s="8">
-        <v>46154.70129416666</v>
+        <v>46154.86796083333</v>
       </c>
       <c r="D37" s="8">
-        <v>46154.70129538194</v>
+        <v>46154.86796204861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>135</v>
@@ -3497,13 +3497,13 @@
         <v>137</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.614640520835</v>
+        <v>46073.7813071875</v>
       </c>
       <c r="C38" s="5">
-        <v>46175.5429012963</v>
+        <v>46175.709567962964</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.49767363426</v>
+        <v>46181.66434030092</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>138</v>
@@ -3546,13 +3546,13 @@
         <v>140</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.61464082176</v>
+        <v>46073.781307488425</v>
       </c>
       <c r="C39" s="8">
-        <v>46098.35299818287</v>
+        <v>46098.51966484953</v>
       </c>
       <c r="D39" s="8">
-        <v>46197.54216777778</v>
+        <v>46197.70883444445</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>141</v>
@@ -3611,13 +3611,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.61463748843</v>
+        <v>46073.7813041551</v>
       </c>
       <c r="C40" s="5">
-        <v>46107.555180509255</v>
+        <v>46107.721847175926</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.49777780093</v>
+        <v>46181.66444446759</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -3676,13 +3676,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46092.33831024305</v>
+        <v>46092.504976909724</v>
       </c>
       <c r="C41" s="8">
-        <v>46107.55534931713</v>
+        <v>46107.722015983796</v>
       </c>
       <c r="D41" s="8">
-        <v>46107.55536530093</v>
+        <v>46107.7220319676</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3741,13 +3741,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46092.33835142361</v>
+        <v>46092.505018090276</v>
       </c>
       <c r="C42" s="5">
-        <v>46175.54288180555</v>
+        <v>46175.70954847222</v>
       </c>
       <c r="D42" s="5">
-        <v>46178.007146516204</v>
+        <v>46178.173813182875</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3806,13 +3806,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.61463778935</v>
+        <v>46073.78130445602</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.610402754624</v>
+        <v>46127.777069421296</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.49773920139</v>
+        <v>46181.664405868054</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3855,13 +3855,13 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.61463805556</v>
+        <v>46073.78130472222</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.48092611111</v>
+        <v>46127.64759277778</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.481235659725</v>
+        <v>46127.64790232639</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -3920,13 +3920,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.61463829861</v>
+        <v>46073.781304965276</v>
       </c>
       <c r="C45" s="8">
-        <v>46127.610388333334</v>
+        <v>46127.777055</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.61040306713</v>
+        <v>46127.7770697338</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -3985,13 +3985,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.61463851852</v>
+        <v>46073.781305185184</v>
       </c>
       <c r="C46" s="5">
-        <v>46157.59841302084</v>
+        <v>46157.765079687495</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.49789353009</v>
+        <v>46181.66456019676</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -4034,13 +4034,13 @@
         <v>176</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.614638750005</v>
+        <v>46073.78130541666</v>
       </c>
       <c r="C47" s="8">
-        <v>46128.32995168981</v>
+        <v>46128.49661835648</v>
       </c>
       <c r="D47" s="8">
-        <v>46128.32996815973</v>
+        <v>46128.496634826384</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>177</v>
@@ -4099,13 +4099,13 @@
         <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.6146390162</v>
+        <v>46073.781305682875</v>
       </c>
       <c r="C48" s="5">
-        <v>46149.72695866898</v>
+        <v>46149.89362533565</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.49785015047</v>
+        <v>46181.66451681713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>182</v>
@@ -4164,13 +4164,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.61463924768</v>
+        <v>46073.78130591435</v>
       </c>
       <c r="C49" s="8">
-        <v>46157.59775716435</v>
+        <v>46157.76442383102</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.4978709375</v>
+        <v>46181.66453760417</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4229,13 +4229,13 @@
         <v>189</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.61463946759</v>
+        <v>46073.78130613426</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.605543032405</v>
+        <v>46157.77220969908</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.60560336805</v>
+        <v>46157.77227003472</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>161</v>
@@ -4278,13 +4278,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.61463969907</v>
+        <v>46073.78130636574</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.60551525463</v>
+        <v>46157.7721819213</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.605530891204</v>
+        <v>46157.772197557875</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4343,13 +4343,13 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.61466482639</v>
+        <v>46073.78133149305</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.605521006946</v>
+        <v>46157.77218767361</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.60553671296</v>
+        <v>46157.77220337963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4408,13 +4408,13 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.61466519676</v>
+        <v>46073.78133186343</v>
       </c>
       <c r="C53" s="8">
-        <v>46157.60552734954</v>
+        <v>46157.7721940162</v>
       </c>
       <c r="D53" s="8">
-        <v>46172.03007071759</v>
+        <v>46172.19673738426</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4473,13 +4473,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.334089525466</v>
+        <v>46077.50075619213</v>
       </c>
       <c r="C54" s="5">
-        <v>46157.602643171296</v>
+        <v>46157.76930983797</v>
       </c>
       <c r="D54" s="5">
-        <v>46157.60265962963</v>
+        <v>46157.7693262963</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4538,13 +4538,13 @@
         <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.61466560185</v>
+        <v>46073.78133226852</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.462844803245</v>
+        <v>46181.6295114699</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.49799682871</v>
+        <v>46181.664663495365</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4587,13 +4587,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.61466594908</v>
+        <v>46073.78133261574</v>
       </c>
       <c r="C56" s="5">
-        <v>46148.27235508102</v>
+        <v>46148.43902174769</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.49814753472</v>
+        <v>46181.66481420139</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4652,13 +4652,13 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.61466634259</v>
+        <v>46073.78133300926</v>
       </c>
       <c r="C57" s="8">
-        <v>46148.27236634259</v>
+        <v>46148.43903300926</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.49818391204</v>
+        <v>46181.6648505787</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>211</v>
@@ -4717,13 +4717,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.61466681713</v>
+        <v>46073.7813334838</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.4627858912</v>
+        <v>46181.62945255787</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.46280165509</v>
+        <v>46181.62946832176</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4782,13 +4782,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.61466721065</v>
+        <v>46073.78133387731</v>
       </c>
       <c r="C59" s="8">
-        <v>46181.462830069446</v>
+        <v>46181.62949673611</v>
       </c>
       <c r="D59" s="8">
-        <v>46181.462844062495</v>
+        <v>46181.629510729166</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4847,13 +4847,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.336303993055</v>
+        <v>46077.50297065973</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.46280292824</v>
+        <v>46181.629469594904</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.46281909722</v>
+        <v>46181.629485763886</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4912,13 +4912,13 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.61466755787</v>
+        <v>46073.781334224535</v>
       </c>
       <c r="C61" s="8">
-        <v>46148.272386111115</v>
+        <v>46148.43905277778</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.49827096065</v>
+        <v>46181.66493762731</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>158</v>
@@ -4975,13 +4975,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.614667905094</v>
+        <v>46073.78133457176</v>
       </c>
       <c r="C62" s="5">
-        <v>46148.27240263889</v>
+        <v>46148.439069305554</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.4983139699</v>
+        <v>46181.664980636575</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>159</v>
@@ -5040,13 +5040,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.61464035879</v>
+        <v>46073.78130702546</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.46211253472</v>
+        <v>46181.62877920139</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.49848010417</v>
+        <v>46181.66514677083</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5089,13 +5089,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.614640740736</v>
+        <v>46073.78130740741</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.4620606713</v>
+        <v>46181.628727337964</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.4620774537</v>
+        <v>46181.628744120375</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5154,13 +5154,13 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.61464101852</v>
+        <v>46073.78130768519</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.46194850694</v>
+        <v>46181.62861517361</v>
       </c>
       <c r="D65" s="8">
-        <v>46183.04071021991</v>
+        <v>46183.207376886574</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5219,13 +5219,13 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.61464130787</v>
+        <v>46073.78130797454</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.46202283565</v>
+        <v>46181.628689502315</v>
       </c>
       <c r="D66" s="5">
-        <v>46183.04071077546</v>
+        <v>46183.20737744213</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>238</v>
@@ -5284,13 +5284,13 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.61464158565</v>
+        <v>46073.78130825231</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.46209758102</v>
+        <v>46181.62876424768</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.01260739584</v>
+        <v>46184.179274062495</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5349,11 +5349,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.614641886576</v>
+        <v>46073.78130855324</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46092.34252207176</v>
+        <v>46092.509188738426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5396,11 +5396,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.61464215278</v>
+        <v>46073.781308819445</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46194.95882381944</v>
+        <v>46195.12549048611</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>247</v>
@@ -5459,11 +5459,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.61464240741</v>
+        <v>46073.781309074075</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46194.95882646991</v>
+        <v>46195.12549313657</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>252</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="251">
   <si>
     <t>50001504 - ZITRON PERU CODESTABLE</t>
   </si>
@@ -226,9 +226,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
   </si>
   <si>
@@ -236,12 +233,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -2284,11 +2275,9 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46034</v>
       </c>
@@ -2311,7 +2300,7 @@
         <v>51</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q18" s="5">
         <v>46034</v>
@@ -2331,7 +2320,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="8">
         <v>46073.781303993055</v>
@@ -2343,17 +2332,15 @@
         <v>46100.70889821759</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>76</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="9"/>
       <c r="I19" s="8">
         <v>46034</v>
       </c>
@@ -2376,7 +2363,7 @@
         <v>54</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q19" s="8">
         <v>46034</v>
@@ -2396,7 +2383,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B20" s="5">
         <v>46077.50058476852</v>
@@ -2408,7 +2395,7 @@
         <v>46114.5275496875</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2441,7 +2428,7 @@
         <v>54</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Q20" s="5">
         <v>46034</v>
@@ -2461,7 +2448,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B21" s="8">
         <v>46073.78130431713</v>
@@ -2473,7 +2460,7 @@
         <v>46181.664278321754</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2497,7 +2484,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2510,7 +2497,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B22" s="5">
         <v>46073.78130459491</v>
@@ -2522,16 +2509,16 @@
         <v>46157.77139890046</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I22" s="5">
         <v>46036</v>
@@ -2549,13 +2536,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q22" s="5">
         <v>46036</v>
@@ -2564,7 +2551,7 @@
         <v>46149</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2575,7 +2562,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B23" s="8">
         <v>46073.78130483796</v>
@@ -2587,16 +2574,16 @@
         <v>46157.77130930556</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I23" s="8">
         <v>46036</v>
@@ -2614,29 +2601,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T23" s="9">
         <v>0</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46073.781305069446</v>
@@ -2648,16 +2635,16 @@
         <v>46157.77137511574</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I24" s="5">
         <v>46038</v>
@@ -2675,29 +2662,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8">
         <v>46073.7813060301</v>
@@ -2709,16 +2696,16 @@
         <v>46157.77155204861</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I25" s="8">
         <v>46036</v>
@@ -2736,13 +2723,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q25" s="8">
         <v>46036</v>
@@ -2762,7 +2749,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46073.781306273144</v>
@@ -2774,16 +2761,16 @@
         <v>46157.77149077546</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I26" s="5">
         <v>46036</v>
@@ -2801,29 +2788,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8">
         <v>46073.78130486111</v>
@@ -2835,16 +2822,16 @@
         <v>46157.77153081019</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I27" s="8">
         <v>46038</v>
@@ -2862,29 +2849,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="O27" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="O27" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="P27" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46073.78130520834</v>
@@ -2896,16 +2883,16 @@
         <v>46170.184024965274</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I28" s="5">
         <v>46024</v>
@@ -2923,13 +2910,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q28" s="5">
         <v>46024</v>
@@ -2949,7 +2936,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B29" s="8">
         <v>46073.78130552083</v>
@@ -2961,16 +2948,16 @@
         <v>46157.771851261576</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I29" s="8">
         <v>46024</v>
@@ -2988,29 +2975,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46073.781305798606</v>
@@ -3022,16 +3009,16 @@
         <v>46157.771893240744</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I30" s="5">
         <v>46044</v>
@@ -3049,29 +3036,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="O30" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="P30" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B31" s="8">
         <v>46073.78130606482</v>
@@ -3083,16 +3070,16 @@
         <v>46157.771915335645</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I31" s="8">
         <v>46044</v>
@@ -3110,29 +3097,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>110</v>
-      </c>
       <c r="P31" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46073.78130635417</v>
@@ -3144,16 +3131,16 @@
         <v>46113.537077800924</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I32" s="5">
         <v>46036</v>
@@ -3171,13 +3158,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q32" s="5">
         <v>46036</v>
@@ -3197,7 +3184,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B33" s="8">
         <v>46073.78130663194</v>
@@ -3209,16 +3196,16 @@
         <v>46097.53415040509</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I33" s="8">
         <v>46036</v>
@@ -3236,29 +3223,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46073.7813069213</v>
@@ -3270,16 +3257,16 @@
         <v>46104.58889570602</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I34" s="5">
         <v>46056</v>
@@ -3297,29 +3284,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B35" s="8">
         <v>46077.50065555556</v>
@@ -3331,16 +3318,16 @@
         <v>46181.66417827546</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I35" s="8">
         <v>46036</v>
@@ -3358,13 +3345,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q35" s="8">
         <v>46036</v>
@@ -3373,7 +3360,7 @@
         <v>46153</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
@@ -3384,7 +3371,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B36" s="5">
         <v>46077.50123298611</v>
@@ -3396,16 +3383,16 @@
         <v>46154.86742951389</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I36" s="5">
         <v>46036</v>
@@ -3423,13 +3410,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P36" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3439,7 +3426,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B37" s="8">
         <v>46077.501358009264</v>
@@ -3451,16 +3438,16 @@
         <v>46154.86796204861</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I37" s="8">
         <v>46076</v>
@@ -3478,13 +3465,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3494,7 +3481,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B38" s="5">
         <v>46073.7813071875</v>
@@ -3506,7 +3493,7 @@
         <v>46181.66434030092</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>25</v>
@@ -3530,7 +3517,7 @@
         <v>26</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3543,7 +3530,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B39" s="8">
         <v>46073.781307488425</v>
@@ -3555,16 +3542,16 @@
         <v>46197.70883444445</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I39" s="8">
         <v>46034</v>
@@ -3582,13 +3569,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>54</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q39" s="8">
         <v>46034</v>
@@ -3597,7 +3584,7 @@
         <v>46038</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -3608,7 +3595,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B40" s="5">
         <v>46073.7813041551</v>
@@ -3620,16 +3607,16 @@
         <v>46181.66444446759</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46084</v>
@@ -3647,13 +3634,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="5">
         <v>46084</v>
@@ -3673,7 +3660,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46092.504976909724</v>
@@ -3685,16 +3672,16 @@
         <v>46107.7220319676</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I41" s="8">
         <v>46091</v>
@@ -3712,13 +3699,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="8">
         <v>46091</v>
@@ -3738,7 +3725,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46092.505018090276</v>
@@ -3750,16 +3737,16 @@
         <v>46178.173813182875</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46177</v>
@@ -3777,13 +3764,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="5">
         <v>46177</v>
@@ -3803,7 +3790,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46073.78130445602</v>
@@ -3815,7 +3802,7 @@
         <v>46181.664405868054</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>25</v>
@@ -3839,7 +3826,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3852,7 +3839,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46073.78130472222</v>
@@ -3864,16 +3851,16 @@
         <v>46127.64790232639</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46085</v>
@@ -3891,13 +3878,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="5">
         <v>46085</v>
@@ -3917,7 +3904,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46073.781304965276</v>
@@ -3929,16 +3916,16 @@
         <v>46127.7770697338</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I45" s="8">
         <v>46087</v>
@@ -3956,13 +3943,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="O45" s="9" t="s">
-        <v>164</v>
-      </c>
       <c r="P45" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="8">
         <v>46087</v>
@@ -3982,7 +3969,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46073.781305185184</v>
@@ -3994,7 +3981,7 @@
         <v>46181.66456019676</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4018,7 +4005,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4031,7 +4018,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B47" s="8">
         <v>46073.78130541666</v>
@@ -4043,16 +4030,16 @@
         <v>46128.496634826384</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I47" s="8">
         <v>46091</v>
@@ -4070,13 +4057,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="8">
         <v>46091</v>
@@ -4096,7 +4083,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46073.781305682875</v>
@@ -4108,16 +4095,16 @@
         <v>46181.66451681713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46100</v>
@@ -4135,13 +4122,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46100</v>
@@ -4161,7 +4148,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B49" s="8">
         <v>46073.78130591435</v>
@@ -4173,16 +4160,16 @@
         <v>46181.66453760417</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I49" s="8">
         <v>46120</v>
@@ -4200,13 +4187,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="8">
         <v>46120</v>
@@ -4226,7 +4213,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46073.78130613426</v>
@@ -4238,7 +4225,7 @@
         <v>46157.77227003472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4262,7 +4249,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4275,7 +4262,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B51" s="8">
         <v>46073.78130636574</v>
@@ -4287,16 +4274,16 @@
         <v>46157.772197557875</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I51" s="8">
         <v>46087</v>
@@ -4314,13 +4301,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="8">
         <v>46087</v>
@@ -4340,7 +4327,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46073.78133149305</v>
@@ -4352,16 +4339,16 @@
         <v>46157.77220337963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I52" s="5">
         <v>46150</v>
@@ -4379,13 +4366,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="5">
         <v>46150</v>
@@ -4394,7 +4381,7 @@
         <v>46153</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -4405,7 +4392,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46073.78133186343</v>
@@ -4417,16 +4404,16 @@
         <v>46172.19673738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I53" s="8">
         <v>46170</v>
@@ -4444,13 +4431,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="8">
         <v>46170</v>
@@ -4470,7 +4457,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46077.50075619213</v>
@@ -4482,16 +4469,16 @@
         <v>46157.7693262963</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I54" s="5">
         <v>46154</v>
@@ -4509,13 +4496,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46154</v>
@@ -4524,7 +4511,7 @@
         <v>46155</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4535,7 +4522,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B55" s="8">
         <v>46073.78133226852</v>
@@ -4547,7 +4534,7 @@
         <v>46181.664663495365</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4571,7 +4558,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4584,7 +4571,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
         <v>46073.78133261574</v>
@@ -4596,17 +4583,15 @@
         <v>46181.66481420139</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H56" s="6"/>
       <c r="I56" s="5">
         <v>46122</v>
       </c>
@@ -4623,13 +4608,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q56" s="5">
         <v>46122</v>
@@ -4638,7 +4623,7 @@
         <v>46141</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4649,7 +4634,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B57" s="8">
         <v>46073.78133300926</v>
@@ -4661,17 +4646,15 @@
         <v>46181.6648505787</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H57" s="9"/>
       <c r="I57" s="8">
         <v>46174</v>
       </c>
@@ -4688,13 +4671,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q57" s="8">
         <v>46174</v>
@@ -4714,7 +4697,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46073.7813334838</v>
@@ -4726,17 +4709,15 @@
         <v>46181.62946832176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H58" s="6"/>
       <c r="I58" s="5">
         <v>46154</v>
       </c>
@@ -4753,13 +4734,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q58" s="5">
         <v>46154</v>
@@ -4768,7 +4749,7 @@
         <v>46155</v>
       </c>
       <c r="S58" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -4779,7 +4760,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B59" s="8">
         <v>46073.78133387731</v>
@@ -4791,17 +4772,15 @@
         <v>46181.629510729166</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H59" s="9"/>
       <c r="I59" s="8">
         <v>46156</v>
       </c>
@@ -4818,13 +4797,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q59" s="8">
         <v>46156</v>
@@ -4844,7 +4823,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46077.50297065973</v>
@@ -4856,17 +4835,15 @@
         <v>46181.629485763886</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H60" s="6"/>
       <c r="I60" s="5">
         <v>46160</v>
       </c>
@@ -4883,13 +4860,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q60" s="5">
         <v>46160</v>
@@ -4909,7 +4886,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B61" s="8">
         <v>46073.781334224535</v>
@@ -4921,17 +4898,15 @@
         <v>46181.66493762731</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H61" s="9"/>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
         <v>46176</v>
@@ -4946,13 +4921,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="8">
         <v>46176</v>
@@ -4972,7 +4947,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46073.78133457176</v>
@@ -4984,17 +4959,15 @@
         <v>46181.664980636575</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H62" s="6"/>
       <c r="I62" s="5">
         <v>46178</v>
       </c>
@@ -5011,13 +4984,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q62" s="5">
         <v>46178</v>
@@ -5037,7 +5010,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B63" s="8">
         <v>46073.78130702546</v>
@@ -5049,7 +5022,7 @@
         <v>46181.66514677083</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5073,7 +5046,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5086,7 +5059,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46073.78130740741</v>
@@ -5098,7 +5071,7 @@
         <v>46181.628744120375</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5125,13 +5098,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="5">
         <v>46178</v>
@@ -5151,7 +5124,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B65" s="8">
         <v>46073.78130768519</v>
@@ -5163,17 +5136,15 @@
         <v>46183.207376886574</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H65" s="9"/>
       <c r="I65" s="8">
         <v>46182</v>
       </c>
@@ -5190,13 +5161,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="O65" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="O65" s="9" t="s">
-        <v>232</v>
-      </c>
       <c r="P65" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="8">
         <v>46181</v>
@@ -5216,7 +5187,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46073.78130797454</v>
@@ -5228,16 +5199,16 @@
         <v>46183.20737744213</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5255,13 +5226,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -5281,7 +5252,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B67" s="8">
         <v>46073.78130825231</v>
@@ -5293,16 +5264,16 @@
         <v>46184.179274062495</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I67" s="8">
         <v>46184</v>
@@ -5320,13 +5291,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="8">
         <v>46183</v>
@@ -5346,7 +5317,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
         <v>46073.78130855324</v>
@@ -5356,7 +5327,7 @@
         <v>46092.509188738426</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5380,7 +5351,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5393,7 +5364,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B69" s="8">
         <v>46073.781308819445</v>
@@ -5403,16 +5374,16 @@
         <v>46195.12549048611</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I69" s="8">
         <v>46185</v>
@@ -5430,13 +5401,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>244</v>
       </c>
       <c r="Q69" s="8">
         <v>46184</v>
@@ -5451,12 +5422,12 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46073.781309074075</v>
@@ -5466,16 +5437,16 @@
         <v>46195.12549313657</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I70" s="5">
         <v>46185</v>
@@ -5493,13 +5464,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q70" s="5">
         <v>46184</v>
@@ -5514,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="252">
   <si>
     <t>50001504 - ZITRON PERU CODESTABLE</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
@@ -2266,7 +2269,7 @@
         <v>46127.61075017361</v>
       </c>
       <c r="D18" s="5">
-        <v>46127.61077237269</v>
+        <v>46223.81883513889</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -2275,9 +2278,11 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I18" s="5">
         <v>46034</v>
       </c>
@@ -2300,7 +2305,7 @@
         <v>51</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="5">
         <v>46034</v>
@@ -2320,7 +2325,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" s="8">
         <v>46073.781303993055</v>
@@ -2329,18 +2334,20 @@
         <v>46097.5340999537</v>
       </c>
       <c r="D19" s="8">
-        <v>46100.70889821759</v>
+        <v>46223.818831979166</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="I19" s="8">
         <v>46034</v>
       </c>
@@ -2363,7 +2370,7 @@
         <v>54</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q19" s="8">
         <v>46034</v>
@@ -2383,7 +2390,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" s="5">
         <v>46077.50058476852</v>
@@ -2395,7 +2402,7 @@
         <v>46114.5275496875</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2428,7 +2435,7 @@
         <v>54</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q20" s="5">
         <v>46034</v>
@@ -2448,7 +2455,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" s="8">
         <v>46073.78130431713</v>
@@ -2460,7 +2467,7 @@
         <v>46181.664278321754</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2484,7 +2491,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2497,7 +2504,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" s="5">
         <v>46073.78130459491</v>
@@ -2509,16 +2516,16 @@
         <v>46157.77139890046</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46036</v>
@@ -2536,13 +2543,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q22" s="5">
         <v>46036</v>
@@ -2551,7 +2558,7 @@
         <v>46149</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2562,7 +2569,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="8">
         <v>46073.78130483796</v>
@@ -2574,16 +2581,16 @@
         <v>46157.77130930556</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I23" s="8">
         <v>46036</v>
@@ -2601,29 +2608,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T23" s="9">
         <v>0</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46073.781305069446</v>
@@ -2635,16 +2642,16 @@
         <v>46157.77137511574</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I24" s="5">
         <v>46038</v>
@@ -2662,29 +2669,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="8">
         <v>46073.7813060301</v>
@@ -2696,16 +2703,16 @@
         <v>46157.77155204861</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I25" s="8">
         <v>46036</v>
@@ -2723,13 +2730,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q25" s="8">
         <v>46036</v>
@@ -2749,7 +2756,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5">
         <v>46073.781306273144</v>
@@ -2761,16 +2768,16 @@
         <v>46157.77149077546</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I26" s="5">
         <v>46036</v>
@@ -2788,29 +2795,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="8">
         <v>46073.78130486111</v>
@@ -2822,16 +2829,16 @@
         <v>46157.77153081019</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I27" s="8">
         <v>46038</v>
@@ -2849,29 +2856,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46073.78130520834</v>
@@ -2883,16 +2890,16 @@
         <v>46170.184024965274</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I28" s="5">
         <v>46024</v>
@@ -2910,13 +2917,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="5">
         <v>46024</v>
@@ -2936,7 +2943,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="8">
         <v>46073.78130552083</v>
@@ -2948,16 +2955,16 @@
         <v>46157.771851261576</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" s="8">
         <v>46024</v>
@@ -2975,29 +2982,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5">
         <v>46073.781305798606</v>
@@ -3009,16 +3016,16 @@
         <v>46157.771893240744</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I30" s="5">
         <v>46044</v>
@@ -3036,29 +3043,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="8">
         <v>46073.78130606482</v>
@@ -3070,16 +3077,16 @@
         <v>46157.771915335645</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I31" s="8">
         <v>46044</v>
@@ -3097,29 +3104,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46073.78130635417</v>
@@ -3131,16 +3138,16 @@
         <v>46113.537077800924</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I32" s="5">
         <v>46036</v>
@@ -3158,13 +3165,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q32" s="5">
         <v>46036</v>
@@ -3184,7 +3191,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="8">
         <v>46073.78130663194</v>
@@ -3196,16 +3203,16 @@
         <v>46097.53415040509</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I33" s="8">
         <v>46036</v>
@@ -3223,29 +3230,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46073.7813069213</v>
@@ -3257,16 +3264,16 @@
         <v>46104.58889570602</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I34" s="5">
         <v>46056</v>
@@ -3284,29 +3291,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="8">
         <v>46077.50065555556</v>
@@ -3318,16 +3325,16 @@
         <v>46181.66417827546</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I35" s="8">
         <v>46036</v>
@@ -3345,13 +3352,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q35" s="8">
         <v>46036</v>
@@ -3360,7 +3367,7 @@
         <v>46153</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
@@ -3371,7 +3378,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46077.50123298611</v>
@@ -3383,16 +3390,16 @@
         <v>46154.86742951389</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I36" s="5">
         <v>46036</v>
@@ -3410,13 +3417,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3426,7 +3433,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B37" s="8">
         <v>46077.501358009264</v>
@@ -3438,16 +3445,16 @@
         <v>46154.86796204861</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I37" s="8">
         <v>46076</v>
@@ -3465,13 +3472,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3481,7 +3488,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B38" s="5">
         <v>46073.7813071875</v>
@@ -3493,7 +3500,7 @@
         <v>46181.66434030092</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>25</v>
@@ -3517,7 +3524,7 @@
         <v>26</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3530,7 +3537,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B39" s="8">
         <v>46073.781307488425</v>
@@ -3542,16 +3549,16 @@
         <v>46197.70883444445</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I39" s="8">
         <v>46034</v>
@@ -3569,13 +3576,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>54</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q39" s="8">
         <v>46034</v>
@@ -3584,7 +3591,7 @@
         <v>46038</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -3595,7 +3602,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B40" s="5">
         <v>46073.7813041551</v>
@@ -3607,16 +3614,16 @@
         <v>46181.66444446759</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46084</v>
@@ -3634,13 +3641,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="5">
         <v>46084</v>
@@ -3660,7 +3667,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46092.504976909724</v>
@@ -3672,16 +3679,16 @@
         <v>46107.7220319676</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I41" s="8">
         <v>46091</v>
@@ -3699,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="8">
         <v>46091</v>
@@ -3725,7 +3732,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46092.505018090276</v>
@@ -3737,16 +3744,16 @@
         <v>46178.173813182875</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46177</v>
@@ -3764,13 +3771,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="5">
         <v>46177</v>
@@ -3790,7 +3797,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46073.78130445602</v>
@@ -3802,7 +3809,7 @@
         <v>46181.664405868054</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>25</v>
@@ -3826,7 +3833,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3839,7 +3846,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46073.78130472222</v>
@@ -3851,16 +3858,16 @@
         <v>46127.64790232639</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I44" s="5">
         <v>46085</v>
@@ -3878,13 +3885,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="5">
         <v>46085</v>
@@ -3904,7 +3911,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46073.781304965276</v>
@@ -3916,16 +3923,16 @@
         <v>46127.7770697338</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I45" s="8">
         <v>46087</v>
@@ -3943,13 +3950,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="8">
         <v>46087</v>
@@ -3969,7 +3976,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46073.781305185184</v>
@@ -3981,7 +3988,7 @@
         <v>46181.66456019676</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4005,7 +4012,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4018,7 +4025,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B47" s="8">
         <v>46073.78130541666</v>
@@ -4030,16 +4037,16 @@
         <v>46128.496634826384</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I47" s="8">
         <v>46091</v>
@@ -4057,13 +4064,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="8">
         <v>46091</v>
@@ -4083,7 +4090,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46073.781305682875</v>
@@ -4095,16 +4102,16 @@
         <v>46181.66451681713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46100</v>
@@ -4122,13 +4129,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46100</v>
@@ -4148,7 +4155,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="8">
         <v>46073.78130591435</v>
@@ -4160,16 +4167,16 @@
         <v>46181.66453760417</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I49" s="8">
         <v>46120</v>
@@ -4187,13 +4194,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q49" s="8">
         <v>46120</v>
@@ -4213,7 +4220,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46073.78130613426</v>
@@ -4225,7 +4232,7 @@
         <v>46157.77227003472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4249,7 +4256,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4262,7 +4269,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46073.78130636574</v>
@@ -4274,16 +4281,16 @@
         <v>46157.772197557875</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I51" s="8">
         <v>46087</v>
@@ -4301,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="8">
         <v>46087</v>
@@ -4327,7 +4334,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46073.78133149305</v>
@@ -4339,16 +4346,16 @@
         <v>46157.77220337963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I52" s="5">
         <v>46150</v>
@@ -4366,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="5">
         <v>46150</v>
@@ -4381,7 +4388,7 @@
         <v>46153</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -4392,7 +4399,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46073.78133186343</v>
@@ -4404,16 +4411,16 @@
         <v>46172.19673738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I53" s="8">
         <v>46170</v>
@@ -4431,13 +4438,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="8">
         <v>46170</v>
@@ -4457,7 +4464,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46077.50075619213</v>
@@ -4469,16 +4476,16 @@
         <v>46157.7693262963</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I54" s="5">
         <v>46154</v>
@@ -4496,13 +4503,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46154</v>
@@ -4511,7 +4518,7 @@
         <v>46155</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4522,7 +4529,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B55" s="8">
         <v>46073.78133226852</v>
@@ -4534,7 +4541,7 @@
         <v>46181.664663495365</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4558,7 +4565,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4571,7 +4578,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46073.78133261574</v>
@@ -4580,18 +4587,20 @@
         <v>46148.43902174769</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.66481420139</v>
+        <v>46223.818953368056</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I56" s="5">
         <v>46122</v>
       </c>
@@ -4608,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q56" s="5">
         <v>46122</v>
@@ -4623,7 +4632,7 @@
         <v>46141</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4634,7 +4643,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B57" s="8">
         <v>46073.78133300926</v>
@@ -4643,18 +4652,20 @@
         <v>46148.43903300926</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.6648505787</v>
+        <v>46223.81894967593</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="I57" s="8">
         <v>46174</v>
       </c>
@@ -4671,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="8">
         <v>46174</v>
@@ -4697,7 +4708,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46073.7813334838</v>
@@ -4706,18 +4717,20 @@
         <v>46181.62945255787</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.62946832176</v>
+        <v>46223.81894628472</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H58" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I58" s="5">
         <v>46154</v>
       </c>
@@ -4734,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q58" s="5">
         <v>46154</v>
@@ -4749,7 +4762,7 @@
         <v>46155</v>
       </c>
       <c r="S58" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -4760,7 +4773,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B59" s="8">
         <v>46073.78133387731</v>
@@ -4769,18 +4782,20 @@
         <v>46181.62949673611</v>
       </c>
       <c r="D59" s="8">
-        <v>46181.629510729166</v>
+        <v>46223.818942673606</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="I59" s="8">
         <v>46156</v>
       </c>
@@ -4797,13 +4812,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="8">
         <v>46156</v>
@@ -4823,7 +4838,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46077.50297065973</v>
@@ -4832,18 +4847,20 @@
         <v>46181.629469594904</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.629485763886</v>
+        <v>46223.818939108794</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I60" s="5">
         <v>46160</v>
       </c>
@@ -4860,13 +4877,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="5">
         <v>46160</v>
@@ -4886,7 +4903,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B61" s="8">
         <v>46073.781334224535</v>
@@ -4895,18 +4912,20 @@
         <v>46148.43905277778</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.66493762731</v>
+        <v>46223.81893504629</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
         <v>46176</v>
@@ -4921,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="8">
         <v>46176</v>
@@ -4947,7 +4966,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46073.78133457176</v>
@@ -4956,18 +4975,20 @@
         <v>46148.439069305554</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.664980636575</v>
+        <v>46223.81892815972</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="I62" s="5">
         <v>46178</v>
       </c>
@@ -4984,13 +5005,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q62" s="5">
         <v>46178</v>
@@ -5010,7 +5031,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B63" s="8">
         <v>46073.78130702546</v>
@@ -5022,7 +5043,7 @@
         <v>46181.66514677083</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5046,7 +5067,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5059,7 +5080,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46073.78130740741</v>
@@ -5071,7 +5092,7 @@
         <v>46181.628744120375</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5098,13 +5119,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q64" s="5">
         <v>46178</v>
@@ -5124,7 +5145,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="8">
         <v>46073.78130768519</v>
@@ -5136,7 +5157,7 @@
         <v>46183.207376886574</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5161,13 +5182,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q65" s="8">
         <v>46181</v>
@@ -5187,7 +5208,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B66" s="5">
         <v>46073.78130797454</v>
@@ -5199,16 +5220,16 @@
         <v>46183.20737744213</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5226,13 +5247,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -5252,7 +5273,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B67" s="8">
         <v>46073.78130825231</v>
@@ -5264,16 +5285,16 @@
         <v>46184.179274062495</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I67" s="8">
         <v>46184</v>
@@ -5291,13 +5312,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q67" s="8">
         <v>46183</v>
@@ -5317,7 +5338,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46073.78130855324</v>
@@ -5327,7 +5348,7 @@
         <v>46092.509188738426</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5351,7 +5372,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5364,7 +5385,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B69" s="8">
         <v>46073.781308819445</v>
@@ -5374,16 +5395,16 @@
         <v>46195.12549048611</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I69" s="8">
         <v>46185</v>
@@ -5401,13 +5422,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q69" s="8">
         <v>46184</v>
@@ -5422,12 +5443,12 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B70" s="5">
         <v>46073.781309074075</v>
@@ -5437,16 +5458,16 @@
         <v>46195.12549313657</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I70" s="5">
         <v>46185</v>
@@ -5464,13 +5485,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q70" s="5">
         <v>46184</v>
@@ -5485,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="252">
   <si>
     <t>50001504 - ZITRON PERU CODESTABLE</t>
   </si>
@@ -5154,7 +5154,7 @@
         <v>46181.62861517361</v>
       </c>
       <c r="D65" s="8">
-        <v>46183.207376886574</v>
+        <v>46223.83450777778</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5163,9 +5163,11 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="I65" s="8">
         <v>46182</v>
       </c>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="253">
   <si>
     <t>50001504 - ZITRON PERU CODESTABLE</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2281,7 +2284,7 @@
         <v>71</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" s="5">
         <v>46034</v>
@@ -2305,7 +2308,7 @@
         <v>51</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q18" s="5">
         <v>46034</v>
@@ -2325,7 +2328,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" s="8">
         <v>46073.781303993055</v>
@@ -2337,7 +2340,7 @@
         <v>46223.818831979166</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2346,7 +2349,7 @@
         <v>71</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I19" s="8">
         <v>46034</v>
@@ -2370,7 +2373,7 @@
         <v>54</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="8">
         <v>46034</v>
@@ -2390,7 +2393,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" s="5">
         <v>46077.50058476852</v>
@@ -2402,7 +2405,7 @@
         <v>46114.5275496875</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2435,7 +2438,7 @@
         <v>54</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="5">
         <v>46034</v>
@@ -2455,7 +2458,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" s="8">
         <v>46073.78130431713</v>
@@ -2467,7 +2470,7 @@
         <v>46181.664278321754</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2491,7 +2494,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2504,7 +2507,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" s="5">
         <v>46073.78130459491</v>
@@ -2516,16 +2519,16 @@
         <v>46157.77139890046</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I22" s="5">
         <v>46036</v>
@@ -2543,13 +2546,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q22" s="5">
         <v>46036</v>
@@ -2558,7 +2561,7 @@
         <v>46149</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2569,7 +2572,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="8">
         <v>46073.78130483796</v>
@@ -2581,16 +2584,16 @@
         <v>46157.77130930556</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I23" s="8">
         <v>46036</v>
@@ -2608,29 +2611,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T23" s="9">
         <v>0</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46073.781305069446</v>
@@ -2642,16 +2645,16 @@
         <v>46157.77137511574</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I24" s="5">
         <v>46038</v>
@@ -2669,29 +2672,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46073.7813060301</v>
@@ -2703,16 +2706,16 @@
         <v>46157.77155204861</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I25" s="8">
         <v>46036</v>
@@ -2730,13 +2733,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q25" s="8">
         <v>46036</v>
@@ -2756,7 +2759,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46073.781306273144</v>
@@ -2768,16 +2771,16 @@
         <v>46157.77149077546</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I26" s="5">
         <v>46036</v>
@@ -2795,29 +2798,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B27" s="8">
         <v>46073.78130486111</v>
@@ -2829,16 +2832,16 @@
         <v>46157.77153081019</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I27" s="8">
         <v>46038</v>
@@ -2856,29 +2859,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" s="5">
         <v>46073.78130520834</v>
@@ -2890,16 +2893,16 @@
         <v>46170.184024965274</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I28" s="5">
         <v>46024</v>
@@ -2917,13 +2920,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q28" s="5">
         <v>46024</v>
@@ -2943,7 +2946,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" s="8">
         <v>46073.78130552083</v>
@@ -2955,16 +2958,16 @@
         <v>46157.771851261576</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I29" s="8">
         <v>46024</v>
@@ -2982,29 +2985,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5">
         <v>46073.781305798606</v>
@@ -3016,16 +3019,16 @@
         <v>46157.771893240744</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I30" s="5">
         <v>46044</v>
@@ -3043,29 +3046,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="8">
         <v>46073.78130606482</v>
@@ -3077,16 +3080,16 @@
         <v>46157.771915335645</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I31" s="8">
         <v>46044</v>
@@ -3104,29 +3107,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46073.78130635417</v>
@@ -3138,16 +3141,16 @@
         <v>46113.537077800924</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I32" s="5">
         <v>46036</v>
@@ -3165,13 +3168,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q32" s="5">
         <v>46036</v>
@@ -3191,7 +3194,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B33" s="8">
         <v>46073.78130663194</v>
@@ -3203,16 +3206,16 @@
         <v>46097.53415040509</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I33" s="8">
         <v>46036</v>
@@ -3230,29 +3233,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46073.7813069213</v>
@@ -3264,16 +3267,16 @@
         <v>46104.58889570602</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I34" s="5">
         <v>46056</v>
@@ -3291,29 +3294,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="8">
         <v>46077.50065555556</v>
@@ -3325,16 +3328,16 @@
         <v>46181.66417827546</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I35" s="8">
         <v>46036</v>
@@ -3352,13 +3355,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q35" s="8">
         <v>46036</v>
@@ -3367,7 +3370,7 @@
         <v>46153</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
@@ -3378,7 +3381,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46077.50123298611</v>
@@ -3390,16 +3393,16 @@
         <v>46154.86742951389</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I36" s="5">
         <v>46036</v>
@@ -3417,13 +3420,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3433,7 +3436,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="8">
         <v>46077.501358009264</v>
@@ -3445,16 +3448,16 @@
         <v>46154.86796204861</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I37" s="8">
         <v>46076</v>
@@ -3472,13 +3475,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3488,7 +3491,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46073.7813071875</v>
@@ -3500,7 +3503,7 @@
         <v>46181.66434030092</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>25</v>
@@ -3524,7 +3527,7 @@
         <v>26</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3537,7 +3540,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>46073.781307488425</v>
@@ -3549,16 +3552,16 @@
         <v>46197.70883444445</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I39" s="8">
         <v>46034</v>
@@ -3576,13 +3579,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>54</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q39" s="8">
         <v>46034</v>
@@ -3591,7 +3594,7 @@
         <v>46038</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -3602,7 +3605,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46073.7813041551</v>
@@ -3614,16 +3617,16 @@
         <v>46181.66444446759</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46084</v>
@@ -3641,13 +3644,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="5">
         <v>46084</v>
@@ -3667,7 +3670,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46092.504976909724</v>
@@ -3679,16 +3682,16 @@
         <v>46107.7220319676</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I41" s="8">
         <v>46091</v>
@@ -3706,13 +3709,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="8">
         <v>46091</v>
@@ -3732,7 +3735,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46092.505018090276</v>
@@ -3744,16 +3747,16 @@
         <v>46178.173813182875</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I42" s="5">
         <v>46177</v>
@@ -3771,13 +3774,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="5">
         <v>46177</v>
@@ -3797,7 +3800,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46073.78130445602</v>
@@ -3809,7 +3812,7 @@
         <v>46181.664405868054</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>25</v>
@@ -3833,7 +3836,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3846,7 +3849,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46073.78130472222</v>
@@ -3858,16 +3861,16 @@
         <v>46127.64790232639</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I44" s="5">
         <v>46085</v>
@@ -3885,13 +3888,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46085</v>
@@ -3911,7 +3914,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46073.781304965276</v>
@@ -3923,16 +3926,16 @@
         <v>46127.7770697338</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I45" s="8">
         <v>46087</v>
@@ -3950,13 +3953,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="8">
         <v>46087</v>
@@ -3976,7 +3979,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46073.781305185184</v>
@@ -3988,7 +3991,7 @@
         <v>46181.66456019676</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4012,7 +4015,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4025,7 +4028,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="8">
         <v>46073.78130541666</v>
@@ -4037,16 +4040,16 @@
         <v>46128.496634826384</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="8">
         <v>46091</v>
@@ -4064,13 +4067,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47" s="8">
         <v>46091</v>
@@ -4090,7 +4093,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46073.781305682875</v>
@@ -4102,16 +4105,16 @@
         <v>46181.66451681713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46100</v>
@@ -4129,13 +4132,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q48" s="5">
         <v>46100</v>
@@ -4155,7 +4158,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B49" s="8">
         <v>46073.78130591435</v>
@@ -4167,16 +4170,16 @@
         <v>46181.66453760417</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I49" s="8">
         <v>46120</v>
@@ -4194,13 +4197,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q49" s="8">
         <v>46120</v>
@@ -4220,7 +4223,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" s="5">
         <v>46073.78130613426</v>
@@ -4232,7 +4235,7 @@
         <v>46157.77227003472</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4256,7 +4259,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4269,7 +4272,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46073.78130636574</v>
@@ -4281,16 +4284,16 @@
         <v>46157.772197557875</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46087</v>
@@ -4308,13 +4311,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="8">
         <v>46087</v>
@@ -4334,7 +4337,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46073.78133149305</v>
@@ -4346,16 +4349,16 @@
         <v>46157.77220337963</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I52" s="5">
         <v>46150</v>
@@ -4373,13 +4376,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46150</v>
@@ -4388,7 +4391,7 @@
         <v>46153</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -4399,7 +4402,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="8">
         <v>46073.78133186343</v>
@@ -4411,16 +4414,16 @@
         <v>46172.19673738426</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I53" s="8">
         <v>46170</v>
@@ -4438,13 +4441,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="8">
         <v>46170</v>
@@ -4464,7 +4467,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46077.50075619213</v>
@@ -4476,16 +4479,16 @@
         <v>46157.7693262963</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I54" s="5">
         <v>46154</v>
@@ -4503,13 +4506,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46154</v>
@@ -4518,7 +4521,7 @@
         <v>46155</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4529,7 +4532,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46073.78133226852</v>
@@ -4541,7 +4544,7 @@
         <v>46181.664663495365</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4565,7 +4568,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4578,7 +4581,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46073.78133261574</v>
@@ -4590,7 +4593,7 @@
         <v>46223.818953368056</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4599,7 +4602,7 @@
         <v>71</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I56" s="5">
         <v>46122</v>
@@ -4617,13 +4620,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q56" s="5">
         <v>46122</v>
@@ -4632,7 +4635,7 @@
         <v>46141</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4643,7 +4646,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B57" s="8">
         <v>46073.78133300926</v>
@@ -4655,7 +4658,7 @@
         <v>46223.81894967593</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -4664,7 +4667,7 @@
         <v>71</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I57" s="8">
         <v>46174</v>
@@ -4682,13 +4685,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="8">
         <v>46174</v>
@@ -4708,7 +4711,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46073.7813334838</v>
@@ -4720,7 +4723,7 @@
         <v>46223.81894628472</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4729,7 +4732,7 @@
         <v>71</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4747,13 +4750,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="5">
         <v>46154</v>
@@ -4762,7 +4765,7 @@
         <v>46155</v>
       </c>
       <c r="S58" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -4773,7 +4776,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46073.78133387731</v>
@@ -4785,7 +4788,7 @@
         <v>46223.818942673606</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4794,7 +4797,7 @@
         <v>71</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I59" s="8">
         <v>46156</v>
@@ -4812,13 +4815,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="8">
         <v>46156</v>
@@ -4838,7 +4841,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46077.50297065973</v>
@@ -4850,7 +4853,7 @@
         <v>46223.818939108794</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4859,7 +4862,7 @@
         <v>71</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I60" s="5">
         <v>46160</v>
@@ -4877,13 +4880,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="5">
         <v>46160</v>
@@ -4903,7 +4906,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="8">
         <v>46073.781334224535</v>
@@ -4915,7 +4918,7 @@
         <v>46223.81893504629</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -4924,7 +4927,7 @@
         <v>71</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -4940,13 +4943,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="8">
         <v>46176</v>
@@ -4966,7 +4969,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46073.78133457176</v>
@@ -4978,7 +4981,7 @@
         <v>46223.81892815972</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4987,7 +4990,7 @@
         <v>71</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I62" s="5">
         <v>46178</v>
@@ -5005,13 +5008,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q62" s="5">
         <v>46178</v>
@@ -5031,7 +5034,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B63" s="8">
         <v>46073.78130702546</v>
@@ -5043,7 +5046,7 @@
         <v>46181.66514677083</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5067,7 +5070,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5080,7 +5083,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46073.78130740741</v>
@@ -5092,7 +5095,7 @@
         <v>46181.628744120375</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5119,13 +5122,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46178</v>
@@ -5145,7 +5148,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B65" s="8">
         <v>46073.78130768519</v>
@@ -5157,7 +5160,7 @@
         <v>46223.83450777778</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5166,7 +5169,7 @@
         <v>71</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I65" s="8">
         <v>46182</v>
@@ -5184,13 +5187,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q65" s="8">
         <v>46181</v>
@@ -5210,7 +5213,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
         <v>46073.78130797454</v>
@@ -5222,16 +5225,16 @@
         <v>46183.20737744213</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5249,13 +5252,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -5275,7 +5278,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="8">
         <v>46073.78130825231</v>
@@ -5287,16 +5290,16 @@
         <v>46184.179274062495</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I67" s="8">
         <v>46184</v>
@@ -5314,13 +5317,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q67" s="8">
         <v>46183</v>
@@ -5340,7 +5343,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46073.78130855324</v>
@@ -5350,7 +5353,7 @@
         <v>46092.509188738426</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5374,7 +5377,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5387,7 +5390,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B69" s="8">
         <v>46073.781308819445</v>
@@ -5397,16 +5400,16 @@
         <v>46195.12549048611</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I69" s="8">
         <v>46185</v>
@@ -5424,13 +5427,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q69" s="8">
         <v>46184</v>
@@ -5445,12 +5448,12 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B70" s="5">
         <v>46073.781309074075</v>
@@ -5460,16 +5463,16 @@
         <v>46195.12549313657</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I70" s="5">
         <v>46185</v>
@@ -5487,13 +5490,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="5">
         <v>46184</v>
@@ -5508,7 +5511,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -2467,7 +2467,7 @@
         <v>46169.82263542824</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.664278321754</v>
+        <v>46228.46496203703</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3809,7 +3809,7 @@
         <v>46127.777069421296</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.664405868054</v>
+        <v>46228.823016215276</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="252">
   <si>
     <t>50001504 - ZITRON PERU CODESTABLE</t>
   </si>
@@ -758,9 +758,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213381355319339</t>
@@ -5348,9 +5345,11 @@
       <c r="B68" s="5">
         <v>46073.78130855324</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46240.60821989583</v>
+      </c>
       <c r="D68" s="5">
-        <v>46092.509188738426</v>
+        <v>46240.60823146991</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>243</v>
@@ -5385,8 +5384,12 @@
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
       <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+      <c r="T68" s="6">
+        <v>1</v>
+      </c>
+      <c r="U68" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
@@ -5395,9 +5398,11 @@
       <c r="B69" s="8">
         <v>46073.781308819445</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="8">
+        <v>46240.608202442134</v>
+      </c>
       <c r="D69" s="8">
-        <v>46195.12549048611</v>
+        <v>46240.60822030093</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>246</v>
@@ -5445,25 +5450,27 @@
         <v>31</v>
       </c>
       <c r="T69" s="9">
-        <v>0</v>
-      </c>
-      <c r="U69" s="12" t="s">
-        <v>249</v>
+        <v>1</v>
+      </c>
+      <c r="U69" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B70" s="5">
         <v>46073.781309074075</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46240.60820809028</v>
+      </c>
       <c r="D70" s="5">
-        <v>46195.12549313657</v>
+        <v>46240.60822408565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5493,7 +5500,7 @@
         <v>243</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>243</v>
@@ -5508,10 +5515,10 @@
         <v>31</v>
       </c>
       <c r="T70" s="6">
-        <v>0</v>
-      </c>
-      <c r="U70" s="12" t="s">
-        <v>249</v>
+        <v>1</v>
+      </c>
+      <c r="U70" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
